--- a/src/templates/gyomu-hokokusho.xlsx
+++ b/src/templates/gyomu-hokokusho.xlsx
@@ -2911,31 +2911,29 @@
       <c r="K9" s="66"/>
       <c r="L9" s="55"/>
       <c r="M9" s="67">
-        <f t="shared" ref="M9" si="6">IF(E9="","",IF((BO9+BQ9)=0,"",(BO9+BQ9)*60))</f>
-        <v>60</v>
+        <f>IF(E9="","",IF((BO9+BQ9)=0,"",(BO9+BQ9)*60))</f>
       </c>
       <c r="N9" s="55"/>
       <c r="O9" s="68">
         <f>IF(E9&lt;&gt;"",IF(BU9&lt;&gt;0,BU9/24,""),"")</f>
-        <v>0.19791666666787933</v>
       </c>
       <c r="P9" s="26"/>
       <c r="Q9" s="26"/>
       <c r="R9" s="55"/>
       <c r="S9" s="68">
-        <f t="shared" ref="S9:S16" si="7">IF(E9&lt;&gt;"",IF(BY9&lt;&gt;0,BY9/24,""),"")</f>
+        <f>IF(E9&lt;&gt;"",IF(BY9&lt;&gt;0,BY9/24,""),"")</f>
       </c>
       <c r="T9" s="26"/>
       <c r="U9" s="26"/>
       <c r="V9" s="55"/>
       <c r="W9" s="68">
-        <f t="shared" ref="W9:W35" si="8">IF(E9&lt;&gt;"",IF(BS9&lt;&gt;0,BS9/24,""),"")</f>
+        <f>IF(E9&lt;&gt;"",IF(BS9&lt;&gt;0,BS9/24,""),"")</f>
       </c>
       <c r="X9" s="26"/>
       <c r="Y9" s="26"/>
       <c r="Z9" s="55"/>
       <c r="AA9" s="68">
-        <f t="shared" ref="AA9:AA22" si="9">IF(E9&lt;&gt;"",IF(CA9&lt;&gt;0,CA9/24,""),"")</f>
+        <f>IF(E9&lt;&gt;"",IF(CA9&lt;&gt;0,CA9/24,""),"")</f>
       </c>
       <c r="AB9" s="26"/>
       <c r="AC9" s="26"/>
@@ -2951,9 +2949,8 @@
       <c r="AM9" s="71"/>
       <c r="AN9" s="72"/>
       <c r="AO9" s="55"/>
-      <c r="AP9" s="73" t="str">
-        <f t="shared" ref="AP9:AP39" si="10">IF(OR(AJ9&lt;&gt;"",AN9&lt;&gt;"",(BV9+BW9)&lt;&gt;0),IF(CD9=1,"","要"),IF(OR(S9&lt;&gt;"",W9&lt;&gt;"",AA9&lt;&gt;""),"申",""))</f>
-        <v>要</v>
+      <c r="AP9" s="73">
+        <f>IF(OR(AJ9&lt;&gt;"",AN9&lt;&gt;"",(BV9+BW9)&lt;&gt;0),IF(CD9=1,"","要"),IF(OR(S9&lt;&gt;"",W9&lt;&gt;"",AA9&lt;&gt;""),"申",""))</f>
       </c>
       <c r="AQ9" s="74" t="s">
         <v>23</v>
@@ -2977,19 +2974,19 @@
       <c r="BB9" s="78"/>
       <c r="BC9" s="3"/>
       <c r="BD9" s="3">
-        <f t="shared" ref="BD9:BD39" si="11">IF(ISERR(DAY(BG9)),1,IF(AND(DATEVALUE(BG9)&gt;=DATEVALUE($BJ$5),DATEVALUE(BG9)&lt;=DATEVALUE($BK$5)),0,1))</f>
+        <f t="shared" ref="BD9:BD39" si="6">IF(ISERR(DAY(BG9)),1,IF(AND(DATEVALUE(BG9)&gt;=DATEVALUE($BJ$5),DATEVALUE(BG9)&lt;=DATEVALUE($BK$5)),0,1))</f>
         <v>0</v>
       </c>
       <c r="BE9" s="11">
-        <f t="shared" ref="BE9:BE19" si="12">IF($I$3=1,$A$3-1,$A$3)</f>
+        <f t="shared" ref="BE9:BE19" si="7">IF($I$3=1,$A$3-1,$A$3)</f>
         <v>2026</v>
       </c>
       <c r="BF9" s="11">
-        <f t="shared" ref="BF9:BF19" si="13">IF($I$3=1,12,IF($B$5=$O$5,IF($B$5&lt;$I$3,$B$5,$B$5-1),$B$5))</f>
+        <f t="shared" ref="BF9:BF19" si="8">IF($I$3=1,12,IF($B$5=$O$5,IF($B$5&lt;$I$3,$B$5,$B$5-1),$B$5))</f>
         <v>8</v>
       </c>
       <c r="BG9" s="11" t="str">
-        <f t="shared" ref="BG9:BG39" si="14">CONCATENATE(BE9,"/",BF9,"/",A9)</f>
+        <f t="shared" ref="BG9:BG39" si="9">CONCATENATE(BE9,"/",BF9,"/",A9)</f>
         <v>2026/8/21</v>
       </c>
       <c r="BH9" s="79">
@@ -2997,91 +2994,91 @@
         <v>1</v>
       </c>
       <c r="BI9" s="11">
-        <f t="shared" ref="BI9:BI39" si="15">IF(OR(AJ9="有給休暇",AJ9="欠勤",AJ9="振替休日",AJ9="特別休暇"),1,0)</f>
+        <f t="shared" ref="BI9:BI39" si="10">IF(OR(AJ9="有給休暇",AJ9="欠勤",AJ9="振替休日",AJ9="特別休暇"),1,0)</f>
         <v>0</v>
       </c>
       <c r="BJ9" s="11">
-        <f t="shared" ref="BJ9:BJ39" si="16">IF(AJ9="振替予定休日出勤",1,0)</f>
+        <f t="shared" ref="BJ9:BJ39" si="11">IF(AJ9="振替予定休日出勤",1,0)</f>
         <v>0</v>
       </c>
       <c r="BK9" s="80">
-        <f t="shared" ref="BK9:BK39" si="17">IF(AJ9="休日出勤",IF(C9="日",1,2),0)</f>
+        <f t="shared" ref="BK9:BK39" si="12">IF(AJ9="休日出勤",IF(C9="日",1,2),0)</f>
         <v>0</v>
       </c>
       <c r="BL9" s="16">
-        <f t="shared" ref="BL9:BL39" si="18">IFERROR(IF(BI9=1,TIME(0,0,0),TIME(E9,G9,0)),TIME(0,0,0))</f>
+        <f t="shared" ref="BL9:BL39" si="13">IFERROR(IF(BI9=1,TIME(0,0,0),TIME(E9,G9,0)),TIME(0,0,0))</f>
         <v>0.5</v>
       </c>
       <c r="BM9" s="31">
-        <f t="shared" ref="BM9:BM39" si="19">IFERROR(IF(BI9=1,TIME(0,0,0),IF(E9&gt;I9,TIME(I9,K9,0)+1,TIME(I9,K9,0))),TIME(0,0,0))</f>
+        <f t="shared" ref="BM9:BM39" si="14">IFERROR(IF(BI9=1,TIME(0,0,0),IF(E9&gt;I9,TIME(I9,K9,0)+1,TIME(I9,K9,0))),TIME(0,0,0))</f>
         <v>0.7395833333321207</v>
       </c>
       <c r="BN9" s="81">
-        <f t="shared" ref="BN9:BQ9" si="20">TEXT(MAX(0,MIN($BM9,BN$7)-MAX($BL9,BN$6)),"h:mm")*24</f>
+        <f t="shared" ref="BN9:BQ9" si="15">TEXT(MAX(0,MIN($BM9,BN$7)-MAX($BL9,BN$6)),"h:mm")*24</f>
         <v>0</v>
       </c>
       <c r="BO9" s="82">
-        <f t="shared" si="20"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="BP9" s="82">
-        <f t="shared" si="20"/>
+        <f t="shared" si="15"/>
         <v>4.75</v>
       </c>
       <c r="BQ9" s="82">
-        <f t="shared" si="20"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="BR9" s="82">
-        <f t="shared" ref="BR9:BR39" si="21">TEXT(MAX(0,MIN($BM9,BR$7)-MAX($BL9,BR$6)),"h:mm")*24-BQ9</f>
+        <f t="shared" ref="BR9:BR39" si="16">TEXT(MAX(0,MIN($BM9,BR$7)-MAX($BL9,BR$6)),"h:mm")*24-BQ9</f>
         <v>0</v>
       </c>
       <c r="BS9" s="82">
-        <f t="shared" ref="BS9:BT9" si="22">TEXT(MAX(0,MIN($BM9,BS$7)-MAX($BL9,BS$6)),"h:mm")*24</f>
+        <f t="shared" ref="BS9:BT9" si="17">TEXT(MAX(0,MIN($BM9,BS$7)-MAX($BL9,BS$6)),"h:mm")*24</f>
         <v>0</v>
       </c>
       <c r="BT9" s="83">
-        <f t="shared" si="22"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="BU9" s="82">
-        <f t="shared" ref="BU9:BU39" si="23">IF(OR(BH9=1,BJ9=1),BN9+BP9,0)</f>
+        <f t="shared" ref="BU9:BU39" si="18">IF(OR(BH9=1,BJ9=1),BN9+BP9,0)</f>
         <v>4.75</v>
       </c>
       <c r="BV9" s="82">
-        <f t="shared" ref="BV9:BV39" si="24">IF(BU9&gt;0,IF(AJ9="遅刻（電車遅延）",0,$BH$3-BU9),0)</f>
+        <f t="shared" ref="BV9:BV39" si="19">IF(BU9&gt;0,IF(AJ9="遅刻（電車遅延）",0,$BH$3-BU9),0)</f>
         <v>3</v>
       </c>
       <c r="BW9" s="82">
-        <f t="shared" ref="BW9:BW39" si="25">IF(AND(BU9&gt;0,BV9=0),IF(MIN($BP$7,BM9)=BM9,($BP$7-BM9)*24,0),0)</f>
+        <f t="shared" ref="BW9:BW39" si="20">IF(AND(BU9&gt;0,BV9=0),IF(MIN($BP$7,BM9)=BM9,($BP$7-BM9)*24,0),0)</f>
         <v>0</v>
       </c>
       <c r="BX9" s="82">
-        <f t="shared" ref="BX9:BX39" si="26">MOD(ROUND(BV9+BW9,2),ROUND($BX$7,2))</f>
+        <f t="shared" ref="BX9:BX39" si="21">MOD(ROUND(BV9+BW9,2),ROUND($BX$7,2))</f>
         <v>0</v>
       </c>
       <c r="BY9" s="82">
-        <f t="shared" ref="BY9:BY39" si="27">IF(OR(BH9=1,BJ9=1),BR9+BT9,IF(C9="日",0,BN9+BP9+BR9+BT9))</f>
+        <f t="shared" ref="BY9:BY39" si="22">IF(OR(BH9=1,BJ9=1),BR9+BT9,IF(C9="日",0,BN9+BP9+BR9+BT9))</f>
         <v>0</v>
       </c>
       <c r="BZ9" s="84">
-        <f t="shared" ref="BZ9:BZ39" si="28">IF(OR(BH9=1,BJ9=1),BS9,0)</f>
+        <f t="shared" ref="BZ9:BZ39" si="23">IF(OR(BH9=1,BJ9=1),BS9,0)</f>
         <v>0</v>
       </c>
       <c r="CA9" s="84">
-        <f t="shared" ref="CA9:CA39" si="29">IF(AND(C9="日",BJ9=0),BN9+BP9+BR9+BT9,0)</f>
+        <f t="shared" ref="CA9:CA39" si="24">IF(AND(C9="日",BJ9=0),BN9+BP9+BR9+BT9,0)</f>
         <v>0</v>
       </c>
       <c r="CB9" s="84">
-        <f t="shared" ref="CB9:CB39" si="30">IF(AND(C9="日",BJ9=0),BS9,0)</f>
+        <f t="shared" ref="CB9:CB39" si="25">IF(AND(C9="日",BJ9=0),BS9,0)</f>
         <v>0</v>
       </c>
       <c r="CC9" s="82">
-        <f t="shared" ref="CC9:CC39" si="31">MOD(ROUND(BY9+BZ9+CA9+CB9,2),ROUND($CC$7,2))</f>
+        <f t="shared" ref="CC9:CC39" si="26">MOD(ROUND(BY9+BZ9+CA9+CB9,2),ROUND($CC$7,2))</f>
         <v>0</v>
       </c>
       <c r="CD9" s="11">
-        <f t="shared" ref="CD9:CD39" si="32">IF(OR(AND(AJ9="直行",AN9="直帰"),AND(AJ9="",AN9="直帰"),AND(AJ9="直行",AN9="")),1,0)</f>
+        <f t="shared" ref="CD9:CD39" si="27">IF(OR(AND(AJ9="直行",AN9="直帰"),AND(AJ9="",AN9="直帰"),AND(AJ9="直行",AN9="")),1,0)</f>
         <v>0</v>
       </c>
       <c r="CE9" s="11"/>
@@ -3106,21 +3103,31 @@
       <c r="J10" s="65"/>
       <c r="K10" s="66"/>
       <c r="L10" s="55"/>
-      <c r="M10" s="67"/>
+      <c r="M10" s="67">
+        <f>IF(E10="","",IF((BO10+BQ10)=0,"",(BO10+BQ10)*60))</f>
+      </c>
       <c r="N10" s="55"/>
-      <c r="O10" s="68"/>
+      <c r="O10" s="68">
+        <f>IF(E10&lt;&gt;"",IF(BU10&lt;&gt;0,BU10/24,""),"")</f>
+      </c>
       <c r="P10" s="26"/>
       <c r="Q10" s="26"/>
       <c r="R10" s="55"/>
-      <c r="S10" s="68"/>
+      <c r="S10" s="68">
+        <f>IF(E10&lt;&gt;"",IF(BY10&lt;&gt;0,BY10/24,""),"")</f>
+      </c>
       <c r="T10" s="26"/>
       <c r="U10" s="26"/>
       <c r="V10" s="55"/>
-      <c r="W10" s="68"/>
+      <c r="W10" s="68">
+        <f>IF(E10&lt;&gt;"",IF(BS10&lt;&gt;0,BS10/24,""),"")</f>
+      </c>
       <c r="X10" s="26"/>
       <c r="Y10" s="26"/>
       <c r="Z10" s="55"/>
-      <c r="AA10" s="68"/>
+      <c r="AA10" s="68">
+        <f>IF(E10&lt;&gt;"",IF(CA10&lt;&gt;0,CA10/24,""),"")</f>
+      </c>
       <c r="AB10" s="26"/>
       <c r="AC10" s="26"/>
       <c r="AD10" s="55"/>
@@ -3136,7 +3143,7 @@
       <c r="AN10" s="72"/>
       <c r="AO10" s="55"/>
       <c r="AP10" s="73">
-        <f t="shared" si="10"/>
+        <f>IF(OR(AJ10&lt;&gt;"",AN10&lt;&gt;"",(BV10+BW10)&lt;&gt;0),IF(CD10=1,"","要"),IF(OR(S10&lt;&gt;"",W10&lt;&gt;"",AA10&lt;&gt;""),"申",""))</f>
       </c>
       <c r="AQ10" s="86" t="s">
         <v>29</v>
@@ -3166,19 +3173,19 @@
       </c>
       <c r="BC10" s="3"/>
       <c r="BD10" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BE10" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="7"/>
         <v>2026</v>
       </c>
       <c r="BF10" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
       <c r="BG10" s="11" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>2026/8/22</v>
       </c>
       <c r="BH10" s="79">
@@ -3186,91 +3193,91 @@
         <v>0</v>
       </c>
       <c r="BI10" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ10" s="11">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BK10" s="80">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BL10" s="16">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="BM10" s="31">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="BN10" s="81">
+        <f t="shared" ref="BN10:BQ10" si="28">TEXT(MAX(0,MIN($BM10,BN$7)-MAX($BL10,BN$6)),"h:mm")*24</f>
+        <v>0</v>
+      </c>
+      <c r="BO10" s="82">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="BP10" s="82">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="BQ10" s="82">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="BR10" s="82">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BK10" s="80">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BL10" s="16">
+      <c r="BS10" s="82">
+        <f t="shared" ref="BS10:BT10" si="29">TEXT(MAX(0,MIN($BM10,BS$7)-MAX($BL10,BS$6)),"h:mm")*24</f>
+        <v>0</v>
+      </c>
+      <c r="BT10" s="83">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="BU10" s="82">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BM10" s="31">
+      <c r="BV10" s="82">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="BN10" s="81">
-        <f t="shared" ref="BN10:BQ10" si="33">TEXT(MAX(0,MIN($BM10,BN$7)-MAX($BL10,BN$6)),"h:mm")*24</f>
-        <v>0</v>
-      </c>
-      <c r="BO10" s="82">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="BP10" s="82">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="BQ10" s="82">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="BR10" s="82">
+      <c r="BW10" s="82">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="BX10" s="82">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="BS10" s="82">
-        <f t="shared" ref="BS10:BT10" si="34">TEXT(MAX(0,MIN($BM10,BS$7)-MAX($BL10,BS$6)),"h:mm")*24</f>
-        <v>0</v>
-      </c>
-      <c r="BT10" s="83">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="BU10" s="82">
+      <c r="BY10" s="82">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BZ10" s="84">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="BV10" s="82">
+      <c r="CA10" s="84">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="BW10" s="82">
+      <c r="CB10" s="84">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="BX10" s="82">
+      <c r="CC10" s="82">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="BY10" s="82">
+      <c r="CD10" s="11">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BZ10" s="84">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="CA10" s="84">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="CB10" s="84">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CC10" s="82">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="CD10" s="11">
-        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="CE10" s="11"/>
@@ -3295,21 +3302,31 @@
       <c r="J11" s="65"/>
       <c r="K11" s="66"/>
       <c r="L11" s="55"/>
-      <c r="M11" s="67"/>
+      <c r="M11" s="67">
+        <f>IF(E11="","",IF((BO11+BQ11)=0,"",(BO11+BQ11)*60))</f>
+      </c>
       <c r="N11" s="55"/>
-      <c r="O11" s="68"/>
+      <c r="O11" s="68">
+        <f>IF(E11&lt;&gt;"",IF(BU11&lt;&gt;0,BU11/24,""),"")</f>
+      </c>
       <c r="P11" s="26"/>
       <c r="Q11" s="26"/>
       <c r="R11" s="55"/>
-      <c r="S11" s="68"/>
+      <c r="S11" s="68">
+        <f>IF(E11&lt;&gt;"",IF(BY11&lt;&gt;0,BY11/24,""),"")</f>
+      </c>
       <c r="T11" s="26"/>
       <c r="U11" s="26"/>
       <c r="V11" s="55"/>
-      <c r="W11" s="68"/>
+      <c r="W11" s="68">
+        <f>IF(E11&lt;&gt;"",IF(BS11&lt;&gt;0,BS11/24,""),"")</f>
+      </c>
       <c r="X11" s="26"/>
       <c r="Y11" s="26"/>
       <c r="Z11" s="55"/>
-      <c r="AA11" s="68"/>
+      <c r="AA11" s="68">
+        <f>IF(E11&lt;&gt;"",IF(CA11&lt;&gt;0,CA11/24,""),"")</f>
+      </c>
       <c r="AB11" s="26"/>
       <c r="AC11" s="26"/>
       <c r="AD11" s="55"/>
@@ -3325,7 +3342,7 @@
       <c r="AN11" s="72"/>
       <c r="AO11" s="55"/>
       <c r="AP11" s="73">
-        <f t="shared" si="10"/>
+        <f>IF(OR(AJ11&lt;&gt;"",AN11&lt;&gt;"",(BV11+BW11)&lt;&gt;0),IF(CD11=1,"","要"),IF(OR(S11&lt;&gt;"",W11&lt;&gt;"",AA11&lt;&gt;""),"申",""))</f>
       </c>
       <c r="AQ11" s="49"/>
       <c r="AR11" s="44"/>
@@ -3353,19 +3370,19 @@
       </c>
       <c r="BC11" s="3"/>
       <c r="BD11" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BE11" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="7"/>
         <v>2026</v>
       </c>
       <c r="BF11" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
       <c r="BG11" s="11" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>2026/8/23</v>
       </c>
       <c r="BH11" s="79">
@@ -3373,91 +3390,91 @@
         <v>0</v>
       </c>
       <c r="BI11" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ11" s="11">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BK11" s="80">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BL11" s="16">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="BM11" s="31">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="BN11" s="81">
+        <f t="shared" ref="BN11:BQ11" si="30">TEXT(MAX(0,MIN($BM11,BN$7)-MAX($BL11,BN$6)),"h:mm")*24</f>
+        <v>0</v>
+      </c>
+      <c r="BO11" s="82">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="BP11" s="82">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="BQ11" s="82">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="BR11" s="82">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BK11" s="80">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BL11" s="16">
+      <c r="BS11" s="82">
+        <f t="shared" ref="BS11:BT11" si="31">TEXT(MAX(0,MIN($BM11,BS$7)-MAX($BL11,BS$6)),"h:mm")*24</f>
+        <v>0</v>
+      </c>
+      <c r="BT11" s="83">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="BU11" s="82">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BM11" s="31">
+      <c r="BV11" s="82">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="BN11" s="81">
-        <f t="shared" ref="BN11:BQ11" si="35">TEXT(MAX(0,MIN($BM11,BN$7)-MAX($BL11,BN$6)),"h:mm")*24</f>
-        <v>0</v>
-      </c>
-      <c r="BO11" s="82">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="BP11" s="82">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="BQ11" s="82">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="BR11" s="82">
+      <c r="BW11" s="82">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="BX11" s="82">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="BS11" s="82">
-        <f t="shared" ref="BS11:BT11" si="36">TEXT(MAX(0,MIN($BM11,BS$7)-MAX($BL11,BS$6)),"h:mm")*24</f>
-        <v>0</v>
-      </c>
-      <c r="BT11" s="83">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="BU11" s="82">
+      <c r="BY11" s="82">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BZ11" s="84">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="BV11" s="82">
+      <c r="CA11" s="84">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="BW11" s="82">
+      <c r="CB11" s="84">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="BX11" s="82">
+      <c r="CC11" s="82">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="BY11" s="82">
+      <c r="CD11" s="11">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BZ11" s="84">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="CA11" s="84">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="CB11" s="84">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CC11" s="82">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="CD11" s="11">
-        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="CE11" s="11"/>
@@ -3487,31 +3504,29 @@
       <c r="K12" s="66"/>
       <c r="L12" s="55"/>
       <c r="M12" s="89">
-        <f t="shared" ref="M12" si="37">IF(E12="","",IF((BO12+BQ12)=0,"",(BO12+BQ12)*60))</f>
-        <v>60</v>
+        <f>IF(E12="","",IF((BO12+BQ12)=0,"",(BO12+BQ12)*60))</f>
       </c>
       <c r="N12" s="55"/>
       <c r="O12" s="68">
-        <f t="shared" ref="O12" si="38">IF(E12&lt;&gt;"",IF(BU12&lt;&gt;0,BU12/24,""),"")</f>
-        <v>0.3229166666678793</v>
+        <f>IF(E12&lt;&gt;"",IF(BU12&lt;&gt;0,BU12/24,""),"")</f>
       </c>
       <c r="P12" s="26"/>
       <c r="Q12" s="26"/>
       <c r="R12" s="55"/>
       <c r="S12" s="68">
-        <f t="shared" si="7"/>
+        <f>IF(E12&lt;&gt;"",IF(BY12&lt;&gt;0,BY12/24,""),"")</f>
       </c>
       <c r="T12" s="26"/>
       <c r="U12" s="26"/>
       <c r="V12" s="55"/>
       <c r="W12" s="68">
-        <f t="shared" si="8"/>
+        <f>IF(E12&lt;&gt;"",IF(BS12&lt;&gt;0,BS12/24,""),"")</f>
       </c>
       <c r="X12" s="26"/>
       <c r="Y12" s="26"/>
       <c r="Z12" s="55"/>
       <c r="AA12" s="68">
-        <f t="shared" si="9"/>
+        <f>IF(E12&lt;&gt;"",IF(CA12&lt;&gt;0,CA12/24,""),"")</f>
       </c>
       <c r="AB12" s="26"/>
       <c r="AC12" s="26"/>
@@ -3528,7 +3543,7 @@
       <c r="AN12" s="72"/>
       <c r="AO12" s="55"/>
       <c r="AP12" s="73">
-        <f t="shared" si="10"/>
+        <f>IF(OR(AJ12&lt;&gt;"",AN12&lt;&gt;"",(BV12+BW12)&lt;&gt;0),IF(CD12=1,"","要"),IF(OR(S12&lt;&gt;"",W12&lt;&gt;"",AA12&lt;&gt;""),"申",""))</f>
       </c>
       <c r="AQ12" s="49"/>
       <c r="AR12" s="44"/>
@@ -3548,19 +3563,19 @@
       <c r="BB12" s="55"/>
       <c r="BC12" s="3"/>
       <c r="BD12" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BE12" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="7"/>
         <v>2026</v>
       </c>
       <c r="BF12" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
       <c r="BG12" s="11" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>2026/8/24</v>
       </c>
       <c r="BH12" s="79">
@@ -3568,91 +3583,91 @@
         <v>1</v>
       </c>
       <c r="BI12" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ12" s="11">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BK12" s="80">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BL12" s="16">
+        <f t="shared" si="13"/>
+        <v>0.375</v>
+      </c>
+      <c r="BM12" s="31">
+        <f t="shared" si="14"/>
+        <v>0.7395833333321207</v>
+      </c>
+      <c r="BN12" s="81">
+        <f t="shared" ref="BN12:BQ12" si="32">TEXT(MAX(0,MIN($BM12,BN$7)-MAX($BL12,BN$6)),"h:mm")*24</f>
+        <v>3</v>
+      </c>
+      <c r="BO12" s="82">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="BP12" s="82">
+        <f t="shared" si="32"/>
+        <v>4.75</v>
+      </c>
+      <c r="BQ12" s="82">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="BR12" s="82">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BK12" s="80">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BL12" s="16">
+      <c r="BS12" s="82">
+        <f t="shared" ref="BS12:BT12" si="33">TEXT(MAX(0,MIN($BM12,BS$7)-MAX($BL12,BS$6)),"h:mm")*24</f>
+        <v>0</v>
+      </c>
+      <c r="BT12" s="83">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BU12" s="82">
         <f t="shared" si="18"/>
-        <v>0.375</v>
-      </c>
-      <c r="BM12" s="31">
+        <v>7.75</v>
+      </c>
+      <c r="BV12" s="82">
         <f t="shared" si="19"/>
-        <v>0.7395833333321207</v>
-      </c>
-      <c r="BN12" s="81">
-        <f t="shared" ref="BN12:BQ12" si="39">TEXT(MAX(0,MIN($BM12,BN$7)-MAX($BL12,BN$6)),"h:mm")*24</f>
-        <v>3</v>
-      </c>
-      <c r="BO12" s="82">
-        <f t="shared" si="39"/>
-        <v>1</v>
-      </c>
-      <c r="BP12" s="82">
-        <f t="shared" si="39"/>
-        <v>4.75</v>
-      </c>
-      <c r="BQ12" s="82">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="BR12" s="82">
+        <v>0</v>
+      </c>
+      <c r="BW12" s="82">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="BX12" s="82">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="BS12" s="82">
-        <f t="shared" ref="BS12:BT12" si="40">TEXT(MAX(0,MIN($BM12,BS$7)-MAX($BL12,BS$6)),"h:mm")*24</f>
-        <v>0</v>
-      </c>
-      <c r="BT12" s="83">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="BU12" s="82">
+      <c r="BY12" s="82">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BZ12" s="84">
         <f t="shared" si="23"/>
-        <v>7.75</v>
-      </c>
-      <c r="BV12" s="82">
+        <v>0</v>
+      </c>
+      <c r="CA12" s="84">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="BW12" s="82">
+      <c r="CB12" s="84">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="BX12" s="82">
+      <c r="CC12" s="82">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="BY12" s="82">
+      <c r="CD12" s="11">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BZ12" s="84">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="CA12" s="84">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="CB12" s="84">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CC12" s="82">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="CD12" s="11">
-        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="CE12" s="11"/>
@@ -3682,31 +3697,29 @@
       <c r="K13" s="66"/>
       <c r="L13" s="55"/>
       <c r="M13" s="89">
-        <f t="shared" ref="M13:M14" si="41">IF(E13="","",IF((BO13+BQ13)=0,"",(BO13+BQ13)*60))</f>
-        <v>60</v>
+        <f>IF(E13="","",IF((BO13+BQ13)=0,"",(BO13+BQ13)*60))</f>
       </c>
       <c r="N13" s="55"/>
       <c r="O13" s="68">
-        <f t="shared" ref="O13:O14" si="42">IF(E13&lt;&gt;"",IF(BU13&lt;&gt;0,BU13/24,""),"")</f>
-        <v>0.3229166666678793</v>
+        <f>IF(E13&lt;&gt;"",IF(BU13&lt;&gt;0,BU13/24,""),"")</f>
       </c>
       <c r="P13" s="26"/>
       <c r="Q13" s="26"/>
       <c r="R13" s="55"/>
       <c r="S13" s="68">
-        <f t="shared" si="7"/>
+        <f>IF(E13&lt;&gt;"",IF(BY13&lt;&gt;0,BY13/24,""),"")</f>
       </c>
       <c r="T13" s="26"/>
       <c r="U13" s="26"/>
       <c r="V13" s="55"/>
       <c r="W13" s="68">
-        <f t="shared" si="8"/>
+        <f>IF(E13&lt;&gt;"",IF(BS13&lt;&gt;0,BS13/24,""),"")</f>
       </c>
       <c r="X13" s="26"/>
       <c r="Y13" s="26"/>
       <c r="Z13" s="55"/>
       <c r="AA13" s="68">
-        <f t="shared" si="9"/>
+        <f>IF(E13&lt;&gt;"",IF(CA13&lt;&gt;0,CA13/24,""),"")</f>
       </c>
       <c r="AB13" s="26"/>
       <c r="AC13" s="26"/>
@@ -3723,7 +3736,7 @@
       <c r="AN13" s="72"/>
       <c r="AO13" s="55"/>
       <c r="AP13" s="73">
-        <f t="shared" si="10"/>
+        <f>IF(OR(AJ13&lt;&gt;"",AN13&lt;&gt;"",(BV13+BW13)&lt;&gt;0),IF(CD13=1,"","要"),IF(OR(S13&lt;&gt;"",W13&lt;&gt;"",AA13&lt;&gt;""),"申",""))</f>
       </c>
       <c r="AQ13" s="49"/>
       <c r="AR13" s="44"/>
@@ -3743,19 +3756,19 @@
       <c r="BB13" s="55"/>
       <c r="BC13" s="3"/>
       <c r="BD13" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BE13" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="7"/>
         <v>2026</v>
       </c>
       <c r="BF13" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
       <c r="BG13" s="11" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>2026/8/25</v>
       </c>
       <c r="BH13" s="79">
@@ -3763,91 +3776,91 @@
         <v>1</v>
       </c>
       <c r="BI13" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ13" s="11">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BK13" s="80">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BL13" s="16">
+        <f t="shared" si="13"/>
+        <v>0.375</v>
+      </c>
+      <c r="BM13" s="31">
+        <f t="shared" si="14"/>
+        <v>0.7395833333321207</v>
+      </c>
+      <c r="BN13" s="81">
+        <f t="shared" ref="BN13:BQ13" si="34">TEXT(MAX(0,MIN($BM13,BN$7)-MAX($BL13,BN$6)),"h:mm")*24</f>
+        <v>3</v>
+      </c>
+      <c r="BO13" s="82">
+        <f t="shared" si="34"/>
+        <v>1</v>
+      </c>
+      <c r="BP13" s="82">
+        <f t="shared" si="34"/>
+        <v>4.75</v>
+      </c>
+      <c r="BQ13" s="82">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BR13" s="82">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BK13" s="80">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BL13" s="16">
+      <c r="BS13" s="82">
+        <f t="shared" ref="BS13:BT13" si="35">TEXT(MAX(0,MIN($BM13,BS$7)-MAX($BL13,BS$6)),"h:mm")*24</f>
+        <v>0</v>
+      </c>
+      <c r="BT13" s="83">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BU13" s="82">
         <f t="shared" si="18"/>
-        <v>0.375</v>
-      </c>
-      <c r="BM13" s="31">
+        <v>7.75</v>
+      </c>
+      <c r="BV13" s="82">
         <f t="shared" si="19"/>
-        <v>0.7395833333321207</v>
-      </c>
-      <c r="BN13" s="81">
-        <f t="shared" ref="BN13:BQ13" si="43">TEXT(MAX(0,MIN($BM13,BN$7)-MAX($BL13,BN$6)),"h:mm")*24</f>
-        <v>3</v>
-      </c>
-      <c r="BO13" s="82">
-        <f t="shared" si="43"/>
-        <v>1</v>
-      </c>
-      <c r="BP13" s="82">
-        <f t="shared" si="43"/>
-        <v>4.75</v>
-      </c>
-      <c r="BQ13" s="82">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="BR13" s="82">
+        <v>0</v>
+      </c>
+      <c r="BW13" s="82">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="BX13" s="82">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="BS13" s="82">
-        <f t="shared" ref="BS13:BT13" si="44">TEXT(MAX(0,MIN($BM13,BS$7)-MAX($BL13,BS$6)),"h:mm")*24</f>
-        <v>0</v>
-      </c>
-      <c r="BT13" s="83">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="BU13" s="82">
+      <c r="BY13" s="82">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BZ13" s="84">
         <f t="shared" si="23"/>
-        <v>7.75</v>
-      </c>
-      <c r="BV13" s="82">
+        <v>0</v>
+      </c>
+      <c r="CA13" s="84">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="BW13" s="82">
+      <c r="CB13" s="84">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="BX13" s="82">
+      <c r="CC13" s="82">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="BY13" s="82">
+      <c r="CD13" s="11">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BZ13" s="84">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="CA13" s="84">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="CB13" s="84">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CC13" s="82">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="CD13" s="11">
-        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="CE13" s="11"/>
@@ -3877,32 +3890,29 @@
       <c r="K14" s="66"/>
       <c r="L14" s="55"/>
       <c r="M14" s="89">
-        <f t="shared" si="41"/>
-        <v>75</v>
+        <f>IF(E14="","",IF((BO14+BQ14)=0,"",(BO14+BQ14)*60))</f>
       </c>
       <c r="N14" s="55"/>
       <c r="O14" s="68">
-        <f t="shared" si="42"/>
-        <v>0.3229166666678793</v>
+        <f>IF(E14&lt;&gt;"",IF(BU14&lt;&gt;0,BU14/24,""),"")</f>
       </c>
       <c r="P14" s="26"/>
       <c r="Q14" s="26"/>
       <c r="R14" s="55"/>
       <c r="S14" s="68">
-        <f t="shared" si="7"/>
-        <v>0.020833333332120674</v>
+        <f>IF(E14&lt;&gt;"",IF(BY14&lt;&gt;0,BY14/24,""),"")</f>
       </c>
       <c r="T14" s="26"/>
       <c r="U14" s="26"/>
       <c r="V14" s="55"/>
       <c r="W14" s="68">
-        <f t="shared" si="8"/>
+        <f>IF(E14&lt;&gt;"",IF(BS14&lt;&gt;0,BS14/24,""),"")</f>
       </c>
       <c r="X14" s="26"/>
       <c r="Y14" s="26"/>
       <c r="Z14" s="55"/>
       <c r="AA14" s="68">
-        <f t="shared" si="9"/>
+        <f>IF(E14&lt;&gt;"",IF(CA14&lt;&gt;0,CA14/24,""),"")</f>
       </c>
       <c r="AB14" s="26"/>
       <c r="AC14" s="26"/>
@@ -3918,9 +3928,8 @@
       <c r="AM14" s="71"/>
       <c r="AN14" s="72"/>
       <c r="AO14" s="55"/>
-      <c r="AP14" s="73" t="str">
-        <f t="shared" si="10"/>
-        <v>申</v>
+      <c r="AP14" s="73">
+        <f>IF(OR(AJ14&lt;&gt;"",AN14&lt;&gt;"",(BV14+BW14)&lt;&gt;0),IF(CD14=1,"","要"),IF(OR(S14&lt;&gt;"",W14&lt;&gt;"",AA14&lt;&gt;""),"申",""))</f>
       </c>
       <c r="AQ14" s="49"/>
       <c r="AR14" s="44"/>
@@ -3940,19 +3949,19 @@
       <c r="BB14" s="55"/>
       <c r="BC14" s="3"/>
       <c r="BD14" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BE14" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="7"/>
         <v>2026</v>
       </c>
       <c r="BF14" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
       <c r="BG14" s="11" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>2026/8/26</v>
       </c>
       <c r="BH14" s="79">
@@ -3960,91 +3969,91 @@
         <v>1</v>
       </c>
       <c r="BI14" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ14" s="11">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BK14" s="80">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BL14" s="16">
+        <f t="shared" si="13"/>
+        <v>0.375</v>
+      </c>
+      <c r="BM14" s="31">
+        <f t="shared" si="14"/>
+        <v>0.7708333333321207</v>
+      </c>
+      <c r="BN14" s="81">
+        <f t="shared" ref="BN14:BQ14" si="36">TEXT(MAX(0,MIN($BM14,BN$7)-MAX($BL14,BN$6)),"h:mm")*24</f>
+        <v>3</v>
+      </c>
+      <c r="BO14" s="82">
+        <f t="shared" si="36"/>
+        <v>1</v>
+      </c>
+      <c r="BP14" s="82">
+        <f t="shared" si="36"/>
+        <v>4.75</v>
+      </c>
+      <c r="BQ14" s="82">
+        <f t="shared" si="36"/>
+        <v>0.25</v>
+      </c>
+      <c r="BR14" s="82">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="BK14" s="80">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BL14" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="BS14" s="82">
+        <f t="shared" ref="BS14:BT14" si="37">TEXT(MAX(0,MIN($BM14,BS$7)-MAX($BL14,BS$6)),"h:mm")*24</f>
+        <v>0</v>
+      </c>
+      <c r="BT14" s="83">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="BU14" s="82">
         <f t="shared" si="18"/>
-        <v>0.375</v>
-      </c>
-      <c r="BM14" s="31">
+        <v>7.75</v>
+      </c>
+      <c r="BV14" s="82">
         <f t="shared" si="19"/>
-        <v>0.7708333333321207</v>
-      </c>
-      <c r="BN14" s="81">
-        <f t="shared" ref="BN14:BQ14" si="45">TEXT(MAX(0,MIN($BM14,BN$7)-MAX($BL14,BN$6)),"h:mm")*24</f>
-        <v>3</v>
-      </c>
-      <c r="BO14" s="82">
-        <f t="shared" si="45"/>
-        <v>1</v>
-      </c>
-      <c r="BP14" s="82">
-        <f t="shared" si="45"/>
-        <v>4.75</v>
-      </c>
-      <c r="BQ14" s="82">
-        <f t="shared" si="45"/>
-        <v>0.25</v>
-      </c>
-      <c r="BR14" s="82">
+        <v>0</v>
+      </c>
+      <c r="BW14" s="82">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="BX14" s="82">
         <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="BY14" s="82">
+        <f t="shared" si="22"/>
         <v>0.5</v>
       </c>
-      <c r="BS14" s="82">
-        <f t="shared" ref="BS14:BT14" si="46">TEXT(MAX(0,MIN($BM14,BS$7)-MAX($BL14,BS$6)),"h:mm")*24</f>
-        <v>0</v>
-      </c>
-      <c r="BT14" s="83">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="BU14" s="82">
+      <c r="BZ14" s="84">
         <f t="shared" si="23"/>
-        <v>7.75</v>
-      </c>
-      <c r="BV14" s="82">
+        <v>0</v>
+      </c>
+      <c r="CA14" s="84">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="BW14" s="82">
+      <c r="CB14" s="84">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="BX14" s="82">
+      <c r="CC14" s="82">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="BY14" s="82">
+      <c r="CD14" s="11">
         <f t="shared" si="27"/>
-        <v>0.5</v>
-      </c>
-      <c r="BZ14" s="84">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="CA14" s="84">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="CB14" s="84">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CC14" s="82">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="CD14" s="11">
-        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="CE14" s="11"/>
@@ -4074,31 +4083,29 @@
       <c r="K15" s="66"/>
       <c r="L15" s="55"/>
       <c r="M15" s="67">
-        <f t="shared" ref="M15:M16" si="47">IF(E15="","",IF((BO15+BQ15)=0,"",(BO15+BQ15)*60))</f>
-        <v>60</v>
+        <f>IF(E15="","",IF((BO15+BQ15)=0,"",(BO15+BQ15)*60))</f>
       </c>
       <c r="N15" s="55"/>
       <c r="O15" s="68">
-        <f t="shared" ref="O15:O16" si="48">IF(E15&lt;&gt;"",IF(BU15&lt;&gt;0,BU15/24,""),"")</f>
-        <v>0.3229166666678793</v>
+        <f>IF(E15&lt;&gt;"",IF(BU15&lt;&gt;0,BU15/24,""),"")</f>
       </c>
       <c r="P15" s="26"/>
       <c r="Q15" s="26"/>
       <c r="R15" s="55"/>
       <c r="S15" s="68">
-        <f t="shared" si="7"/>
+        <f>IF(E15&lt;&gt;"",IF(BY15&lt;&gt;0,BY15/24,""),"")</f>
       </c>
       <c r="T15" s="26"/>
       <c r="U15" s="26"/>
       <c r="V15" s="55"/>
       <c r="W15" s="68">
-        <f t="shared" si="8"/>
+        <f>IF(E15&lt;&gt;"",IF(BS15&lt;&gt;0,BS15/24,""),"")</f>
       </c>
       <c r="X15" s="26"/>
       <c r="Y15" s="26"/>
       <c r="Z15" s="55"/>
       <c r="AA15" s="68">
-        <f t="shared" si="9"/>
+        <f>IF(E15&lt;&gt;"",IF(CA15&lt;&gt;0,CA15/24,""),"")</f>
       </c>
       <c r="AB15" s="26"/>
       <c r="AC15" s="26"/>
@@ -4115,7 +4122,7 @@
       <c r="AN15" s="72"/>
       <c r="AO15" s="55"/>
       <c r="AP15" s="73">
-        <f t="shared" si="10"/>
+        <f>IF(OR(AJ15&lt;&gt;"",AN15&lt;&gt;"",(BV15+BW15)&lt;&gt;0),IF(CD15=1,"","要"),IF(OR(S15&lt;&gt;"",W15&lt;&gt;"",AA15&lt;&gt;""),"申",""))</f>
       </c>
       <c r="AQ15" s="47"/>
       <c r="AR15" s="48"/>
@@ -4135,19 +4142,19 @@
       <c r="BB15" s="55"/>
       <c r="BC15" s="3"/>
       <c r="BD15" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BE15" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="7"/>
         <v>2026</v>
       </c>
       <c r="BF15" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
       <c r="BG15" s="11" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>2026/8/27</v>
       </c>
       <c r="BH15" s="79">
@@ -4155,91 +4162,91 @@
         <v>1</v>
       </c>
       <c r="BI15" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ15" s="11">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BK15" s="80">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BL15" s="16">
+        <f t="shared" si="13"/>
+        <v>0.375</v>
+      </c>
+      <c r="BM15" s="31">
+        <f t="shared" si="14"/>
+        <v>0.7395833333321207</v>
+      </c>
+      <c r="BN15" s="81">
+        <f t="shared" ref="BN15:BQ15" si="38">TEXT(MAX(0,MIN($BM15,BN$7)-MAX($BL15,BN$6)),"h:mm")*24</f>
+        <v>3</v>
+      </c>
+      <c r="BO15" s="82">
+        <f t="shared" si="38"/>
+        <v>1</v>
+      </c>
+      <c r="BP15" s="82">
+        <f t="shared" si="38"/>
+        <v>4.75</v>
+      </c>
+      <c r="BQ15" s="82">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="BR15" s="82">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BK15" s="80">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BL15" s="16">
+      <c r="BS15" s="82">
+        <f t="shared" ref="BS15:BT15" si="39">TEXT(MAX(0,MIN($BM15,BS$7)-MAX($BL15,BS$6)),"h:mm")*24</f>
+        <v>0</v>
+      </c>
+      <c r="BT15" s="83">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="BU15" s="82">
         <f t="shared" si="18"/>
-        <v>0.375</v>
-      </c>
-      <c r="BM15" s="31">
+        <v>7.75</v>
+      </c>
+      <c r="BV15" s="82">
         <f t="shared" si="19"/>
-        <v>0.7395833333321207</v>
-      </c>
-      <c r="BN15" s="81">
-        <f t="shared" ref="BN15:BQ15" si="49">TEXT(MAX(0,MIN($BM15,BN$7)-MAX($BL15,BN$6)),"h:mm")*24</f>
-        <v>3</v>
-      </c>
-      <c r="BO15" s="82">
-        <f t="shared" si="49"/>
-        <v>1</v>
-      </c>
-      <c r="BP15" s="82">
-        <f t="shared" si="49"/>
-        <v>4.75</v>
-      </c>
-      <c r="BQ15" s="82">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="BR15" s="82">
+        <v>0</v>
+      </c>
+      <c r="BW15" s="82">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="BX15" s="82">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="BS15" s="82">
-        <f t="shared" ref="BS15:BT15" si="50">TEXT(MAX(0,MIN($BM15,BS$7)-MAX($BL15,BS$6)),"h:mm")*24</f>
-        <v>0</v>
-      </c>
-      <c r="BT15" s="83">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="BU15" s="82">
+      <c r="BY15" s="82">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BZ15" s="84">
         <f t="shared" si="23"/>
-        <v>7.75</v>
-      </c>
-      <c r="BV15" s="82">
+        <v>0</v>
+      </c>
+      <c r="CA15" s="84">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="BW15" s="82">
+      <c r="CB15" s="84">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="BX15" s="82">
+      <c r="CC15" s="82">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="BY15" s="82">
+      <c r="CD15" s="11">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BZ15" s="84">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="CA15" s="84">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="CB15" s="84">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CC15" s="82">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="CD15" s="11">
-        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="CE15" s="11"/>
@@ -4269,31 +4276,29 @@
       <c r="K16" s="66"/>
       <c r="L16" s="55"/>
       <c r="M16" s="67">
-        <f t="shared" si="47"/>
-        <v>60</v>
+        <f>IF(E16="","",IF((BO16+BQ16)=0,"",(BO16+BQ16)*60))</f>
       </c>
       <c r="N16" s="55"/>
       <c r="O16" s="68">
-        <f t="shared" si="48"/>
-        <v>0.3229166666678793</v>
+        <f>IF(E16&lt;&gt;"",IF(BU16&lt;&gt;0,BU16/24,""),"")</f>
       </c>
       <c r="P16" s="26"/>
       <c r="Q16" s="26"/>
       <c r="R16" s="55"/>
       <c r="S16" s="68">
-        <f t="shared" si="7"/>
+        <f>IF(E16&lt;&gt;"",IF(BY16&lt;&gt;0,BY16/24,""),"")</f>
       </c>
       <c r="T16" s="26"/>
       <c r="U16" s="26"/>
       <c r="V16" s="55"/>
       <c r="W16" s="68">
-        <f t="shared" si="8"/>
+        <f>IF(E16&lt;&gt;"",IF(BS16&lt;&gt;0,BS16/24,""),"")</f>
       </c>
       <c r="X16" s="26"/>
       <c r="Y16" s="26"/>
       <c r="Z16" s="55"/>
       <c r="AA16" s="68">
-        <f t="shared" si="9"/>
+        <f>IF(E16&lt;&gt;"",IF(CA16&lt;&gt;0,CA16/24,""),"")</f>
       </c>
       <c r="AB16" s="26"/>
       <c r="AC16" s="26"/>
@@ -4310,7 +4315,7 @@
       <c r="AN16" s="72"/>
       <c r="AO16" s="55"/>
       <c r="AP16" s="73">
-        <f t="shared" si="10"/>
+        <f>IF(OR(AJ16&lt;&gt;"",AN16&lt;&gt;"",(BV16+BW16)&lt;&gt;0),IF(CD16=1,"","要"),IF(OR(S16&lt;&gt;"",W16&lt;&gt;"",AA16&lt;&gt;""),"申",""))</f>
       </c>
       <c r="AQ16" s="54" t="s">
         <v>79</v>
@@ -4336,19 +4341,19 @@
       </c>
       <c r="BC16" s="3"/>
       <c r="BD16" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BE16" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="7"/>
         <v>2026</v>
       </c>
       <c r="BF16" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
       <c r="BG16" s="11" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>2026/8/28</v>
       </c>
       <c r="BH16" s="79">
@@ -4356,91 +4361,91 @@
         <v>1</v>
       </c>
       <c r="BI16" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ16" s="11">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BK16" s="80">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BL16" s="16">
+        <f t="shared" si="13"/>
+        <v>0.375</v>
+      </c>
+      <c r="BM16" s="31">
+        <f t="shared" si="14"/>
+        <v>0.7395833333321207</v>
+      </c>
+      <c r="BN16" s="81">
+        <f t="shared" ref="BN16:BQ16" si="40">TEXT(MAX(0,MIN($BM16,BN$7)-MAX($BL16,BN$6)),"h:mm")*24</f>
+        <v>3</v>
+      </c>
+      <c r="BO16" s="82">
+        <f t="shared" si="40"/>
+        <v>1</v>
+      </c>
+      <c r="BP16" s="82">
+        <f t="shared" si="40"/>
+        <v>4.75</v>
+      </c>
+      <c r="BQ16" s="82">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="BR16" s="82">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BK16" s="80">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BL16" s="16">
+      <c r="BS16" s="82">
+        <f t="shared" ref="BS16:BT16" si="41">TEXT(MAX(0,MIN($BM16,BS$7)-MAX($BL16,BS$6)),"h:mm")*24</f>
+        <v>0</v>
+      </c>
+      <c r="BT16" s="83">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="BU16" s="82">
         <f t="shared" si="18"/>
-        <v>0.375</v>
-      </c>
-      <c r="BM16" s="31">
+        <v>7.75</v>
+      </c>
+      <c r="BV16" s="82">
         <f t="shared" si="19"/>
-        <v>0.7395833333321207</v>
-      </c>
-      <c r="BN16" s="81">
-        <f t="shared" ref="BN16:BQ16" si="51">TEXT(MAX(0,MIN($BM16,BN$7)-MAX($BL16,BN$6)),"h:mm")*24</f>
-        <v>3</v>
-      </c>
-      <c r="BO16" s="82">
-        <f t="shared" si="51"/>
-        <v>1</v>
-      </c>
-      <c r="BP16" s="82">
-        <f t="shared" si="51"/>
-        <v>4.75</v>
-      </c>
-      <c r="BQ16" s="82">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="BR16" s="82">
+        <v>0</v>
+      </c>
+      <c r="BW16" s="82">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="BX16" s="82">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="BS16" s="82">
-        <f t="shared" ref="BS16:BT16" si="52">TEXT(MAX(0,MIN($BM16,BS$7)-MAX($BL16,BS$6)),"h:mm")*24</f>
-        <v>0</v>
-      </c>
-      <c r="BT16" s="83">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="BU16" s="82">
+      <c r="BY16" s="82">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BZ16" s="84">
         <f t="shared" si="23"/>
-        <v>7.75</v>
-      </c>
-      <c r="BV16" s="82">
+        <v>0</v>
+      </c>
+      <c r="CA16" s="84">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="BW16" s="82">
+      <c r="CB16" s="84">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="BX16" s="82">
+      <c r="CC16" s="82">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="BY16" s="82">
+      <c r="CD16" s="11">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BZ16" s="84">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="CA16" s="84">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="CB16" s="84">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CC16" s="82">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="CD16" s="11">
-        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="CE16" s="11"/>
@@ -4469,21 +4474,31 @@
       <c r="J17" s="65"/>
       <c r="K17" s="66"/>
       <c r="L17" s="55"/>
-      <c r="M17" s="67"/>
+      <c r="M17" s="67">
+        <f>IF(E17="","",IF((BO17+BQ17)=0,"",(BO17+BQ17)*60))</f>
+      </c>
       <c r="N17" s="55"/>
-      <c r="O17" s="68"/>
+      <c r="O17" s="68">
+        <f>IF(E17&lt;&gt;"",IF(BU17&lt;&gt;0,BU17/24,""),"")</f>
+      </c>
       <c r="P17" s="26"/>
       <c r="Q17" s="26"/>
       <c r="R17" s="55"/>
-      <c r="S17" s="68"/>
+      <c r="S17" s="68">
+        <f>IF(E17&lt;&gt;"",IF(BY17&lt;&gt;0,BY17/24,""),"")</f>
+      </c>
       <c r="T17" s="26"/>
       <c r="U17" s="26"/>
       <c r="V17" s="55"/>
-      <c r="W17" s="68"/>
+      <c r="W17" s="68">
+        <f>IF(E17&lt;&gt;"",IF(BS17&lt;&gt;0,BS17/24,""),"")</f>
+      </c>
       <c r="X17" s="26"/>
       <c r="Y17" s="26"/>
       <c r="Z17" s="55"/>
-      <c r="AA17" s="68"/>
+      <c r="AA17" s="68">
+        <f>IF(E17&lt;&gt;"",IF(CA17&lt;&gt;0,CA17/24,""),"")</f>
+      </c>
       <c r="AB17" s="26"/>
       <c r="AC17" s="26"/>
       <c r="AD17" s="55"/>
@@ -4499,7 +4514,7 @@
       <c r="AN17" s="72"/>
       <c r="AO17" s="55"/>
       <c r="AP17" s="73">
-        <f t="shared" si="10"/>
+        <f>IF(OR(AJ17&lt;&gt;"",AN17&lt;&gt;"",(BV17+BW17)&lt;&gt;0),IF(CD17=1,"","要"),IF(OR(S17&lt;&gt;"",W17&lt;&gt;"",AA17&lt;&gt;""),"申",""))</f>
       </c>
       <c r="AQ17" s="54" t="s">
         <v>81</v>
@@ -4525,19 +4540,19 @@
       </c>
       <c r="BC17" s="3"/>
       <c r="BD17" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BE17" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="7"/>
         <v>2026</v>
       </c>
       <c r="BF17" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
       <c r="BG17" s="11" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>2026/8/29</v>
       </c>
       <c r="BH17" s="79">
@@ -4545,91 +4560,91 @@
         <v>0</v>
       </c>
       <c r="BI17" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ17" s="11">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BK17" s="80">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BL17" s="16">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="BM17" s="31">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="BN17" s="81">
+        <f t="shared" ref="BN17:BQ17" si="42">TEXT(MAX(0,MIN($BM17,BN$7)-MAX($BL17,BN$6)),"h:mm")*24</f>
+        <v>0</v>
+      </c>
+      <c r="BO17" s="82">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="BP17" s="82">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="BQ17" s="82">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="BR17" s="82">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BK17" s="80">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BL17" s="16">
+      <c r="BS17" s="82">
+        <f t="shared" ref="BS17:BT17" si="43">TEXT(MAX(0,MIN($BM17,BS$7)-MAX($BL17,BS$6)),"h:mm")*24</f>
+        <v>0</v>
+      </c>
+      <c r="BT17" s="83">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="BU17" s="82">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BM17" s="31">
+      <c r="BV17" s="82">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="BN17" s="81">
-        <f t="shared" ref="BN17:BQ17" si="53">TEXT(MAX(0,MIN($BM17,BN$7)-MAX($BL17,BN$6)),"h:mm")*24</f>
-        <v>0</v>
-      </c>
-      <c r="BO17" s="82">
-        <f t="shared" si="53"/>
-        <v>0</v>
-      </c>
-      <c r="BP17" s="82">
-        <f t="shared" si="53"/>
-        <v>0</v>
-      </c>
-      <c r="BQ17" s="82">
-        <f t="shared" si="53"/>
-        <v>0</v>
-      </c>
-      <c r="BR17" s="82">
+      <c r="BW17" s="82">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="BX17" s="82">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="BS17" s="82">
-        <f t="shared" ref="BS17:BT17" si="54">TEXT(MAX(0,MIN($BM17,BS$7)-MAX($BL17,BS$6)),"h:mm")*24</f>
-        <v>0</v>
-      </c>
-      <c r="BT17" s="83">
-        <f t="shared" si="54"/>
-        <v>0</v>
-      </c>
-      <c r="BU17" s="82">
+      <c r="BY17" s="82">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BZ17" s="84">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="BV17" s="82">
+      <c r="CA17" s="84">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="BW17" s="82">
+      <c r="CB17" s="84">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="BX17" s="82">
+      <c r="CC17" s="82">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="BY17" s="82">
+      <c r="CD17" s="11">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BZ17" s="84">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="CA17" s="84">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="CB17" s="84">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CC17" s="82">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="CD17" s="11">
-        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="CE17" s="11"/>
@@ -4658,21 +4673,31 @@
       <c r="J18" s="65"/>
       <c r="K18" s="66"/>
       <c r="L18" s="55"/>
-      <c r="M18" s="89"/>
+      <c r="M18" s="89">
+        <f>IF(E18="","",IF((BO18+BQ18)=0,"",(BO18+BQ18)*60))</f>
+      </c>
       <c r="N18" s="55"/>
-      <c r="O18" s="93"/>
+      <c r="O18" s="93">
+        <f>IF(E18&lt;&gt;"",IF(BU18&lt;&gt;0,BU18/24,""),"")</f>
+      </c>
       <c r="P18" s="26"/>
       <c r="Q18" s="26"/>
       <c r="R18" s="55"/>
-      <c r="S18" s="68"/>
+      <c r="S18" s="68">
+        <f>IF(E18&lt;&gt;"",IF(BY18&lt;&gt;0,BY18/24,""),"")</f>
+      </c>
       <c r="T18" s="26"/>
       <c r="U18" s="26"/>
       <c r="V18" s="55"/>
-      <c r="W18" s="68"/>
+      <c r="W18" s="68">
+        <f>IF(E18&lt;&gt;"",IF(BS18&lt;&gt;0,BS18/24,""),"")</f>
+      </c>
       <c r="X18" s="26"/>
       <c r="Y18" s="26"/>
       <c r="Z18" s="55"/>
-      <c r="AA18" s="68"/>
+      <c r="AA18" s="68">
+        <f>IF(E18&lt;&gt;"",IF(CA18&lt;&gt;0,CA18/24,""),"")</f>
+      </c>
       <c r="AB18" s="26"/>
       <c r="AC18" s="26"/>
       <c r="AD18" s="55"/>
@@ -4688,7 +4713,7 @@
       <c r="AN18" s="72"/>
       <c r="AO18" s="55"/>
       <c r="AP18" s="73">
-        <f t="shared" si="10"/>
+        <f>IF(OR(AJ18&lt;&gt;"",AN18&lt;&gt;"",(BV18+BW18)&lt;&gt;0),IF(CD18=1,"","要"),IF(OR(S18&lt;&gt;"",W18&lt;&gt;"",AA18&lt;&gt;""),"申",""))</f>
       </c>
       <c r="AQ18" s="94" t="s">
         <v>82</v>
@@ -4706,19 +4731,19 @@
       <c r="BB18" s="37"/>
       <c r="BC18" s="3"/>
       <c r="BD18" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BE18" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="7"/>
         <v>2026</v>
       </c>
       <c r="BF18" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
       <c r="BG18" s="11" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>2026/8/30</v>
       </c>
       <c r="BH18" s="79">
@@ -4726,91 +4751,91 @@
         <v>0</v>
       </c>
       <c r="BI18" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ18" s="11">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BK18" s="80">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BL18" s="16">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="BM18" s="31">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="BN18" s="81">
+        <f t="shared" ref="BN18:BQ18" si="44">TEXT(MAX(0,MIN($BM18,BN$7)-MAX($BL18,BN$6)),"h:mm")*24</f>
+        <v>0</v>
+      </c>
+      <c r="BO18" s="82">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="BP18" s="82">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="BQ18" s="82">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="BR18" s="82">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BK18" s="80">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BL18" s="16">
+      <c r="BS18" s="82">
+        <f t="shared" ref="BS18:BT18" si="45">TEXT(MAX(0,MIN($BM18,BS$7)-MAX($BL18,BS$6)),"h:mm")*24</f>
+        <v>0</v>
+      </c>
+      <c r="BT18" s="83">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="BU18" s="82">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BM18" s="31">
+      <c r="BV18" s="82">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="BN18" s="81">
-        <f t="shared" ref="BN18:BQ18" si="55">TEXT(MAX(0,MIN($BM18,BN$7)-MAX($BL18,BN$6)),"h:mm")*24</f>
-        <v>0</v>
-      </c>
-      <c r="BO18" s="82">
-        <f t="shared" si="55"/>
-        <v>0</v>
-      </c>
-      <c r="BP18" s="82">
-        <f t="shared" si="55"/>
-        <v>0</v>
-      </c>
-      <c r="BQ18" s="82">
-        <f t="shared" si="55"/>
-        <v>0</v>
-      </c>
-      <c r="BR18" s="82">
+      <c r="BW18" s="82">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="BX18" s="82">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="BS18" s="82">
-        <f t="shared" ref="BS18:BT18" si="56">TEXT(MAX(0,MIN($BM18,BS$7)-MAX($BL18,BS$6)),"h:mm")*24</f>
-        <v>0</v>
-      </c>
-      <c r="BT18" s="83">
-        <f t="shared" si="56"/>
-        <v>0</v>
-      </c>
-      <c r="BU18" s="82">
+      <c r="BY18" s="82">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BZ18" s="84">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="BV18" s="82">
+      <c r="CA18" s="84">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="BW18" s="82">
+      <c r="CB18" s="84">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="BX18" s="82">
+      <c r="CC18" s="82">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="BY18" s="82">
+      <c r="CD18" s="11">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BZ18" s="84">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="CA18" s="84">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="CB18" s="84">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CC18" s="82">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="CD18" s="11">
-        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="CE18" s="11"/>
@@ -4840,29 +4865,29 @@
       <c r="K19" s="66"/>
       <c r="L19" s="55"/>
       <c r="M19" s="89">
-        <f t="shared" ref="M19" si="57">IF(E19="","",IF((BO19+BQ19)=0,"",(BO19+BQ19)*60))</f>
-        <v>60</v>
+        <f>IF(E19="","",IF((BO19+BQ19)=0,"",(BO19+BQ19)*60))</f>
       </c>
       <c r="N19" s="55"/>
       <c r="O19" s="68">
-        <f t="shared" ref="O19:O23" si="58">IF(E19&lt;&gt;"",IF(BU19&lt;&gt;0,BU19/24,""),"")</f>
-        <v>0.3229166666678793</v>
+        <f>IF(E19&lt;&gt;"",IF(BU19&lt;&gt;0,BU19/24,""),"")</f>
       </c>
       <c r="P19" s="26"/>
       <c r="Q19" s="26"/>
       <c r="R19" s="55"/>
-      <c r="S19" s="68"/>
+      <c r="S19" s="68">
+        <f>IF(E19&lt;&gt;"",IF(BY19&lt;&gt;0,BY19/24,""),"")</f>
+      </c>
       <c r="T19" s="26"/>
       <c r="U19" s="26"/>
       <c r="V19" s="55"/>
       <c r="W19" s="68">
-        <f t="shared" si="8"/>
+        <f>IF(E19&lt;&gt;"",IF(BS19&lt;&gt;0,BS19/24,""),"")</f>
       </c>
       <c r="X19" s="26"/>
       <c r="Y19" s="26"/>
       <c r="Z19" s="55"/>
       <c r="AA19" s="68">
-        <f t="shared" si="9"/>
+        <f>IF(E19&lt;&gt;"",IF(CA19&lt;&gt;0,CA19/24,""),"")</f>
       </c>
       <c r="AB19" s="26"/>
       <c r="AC19" s="26"/>
@@ -4879,7 +4904,7 @@
       <c r="AN19" s="72"/>
       <c r="AO19" s="55"/>
       <c r="AP19" s="73">
-        <f t="shared" si="10"/>
+        <f>IF(OR(AJ19&lt;&gt;"",AN19&lt;&gt;"",(BV19+BW19)&lt;&gt;0),IF(CD19=1,"","要"),IF(OR(S19&lt;&gt;"",W19&lt;&gt;"",AA19&lt;&gt;""),"申",""))</f>
       </c>
       <c r="AQ19" s="47"/>
       <c r="AR19" s="14"/>
@@ -4895,19 +4920,19 @@
       <c r="BB19" s="48"/>
       <c r="BC19" s="3"/>
       <c r="BD19" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BE19" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="7"/>
         <v>2026</v>
       </c>
       <c r="BF19" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
       <c r="BG19" s="11" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>2026/8/31</v>
       </c>
       <c r="BH19" s="79">
@@ -4915,91 +4940,91 @@
         <v>1</v>
       </c>
       <c r="BI19" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ19" s="11">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BK19" s="80">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BL19" s="16">
+        <f t="shared" si="13"/>
+        <v>0.375</v>
+      </c>
+      <c r="BM19" s="31">
+        <f t="shared" si="14"/>
+        <v>0.7395833333321207</v>
+      </c>
+      <c r="BN19" s="81">
+        <f t="shared" ref="BN19:BQ19" si="46">TEXT(MAX(0,MIN($BM19,BN$7)-MAX($BL19,BN$6)),"h:mm")*24</f>
+        <v>3</v>
+      </c>
+      <c r="BO19" s="82">
+        <f t="shared" si="46"/>
+        <v>1</v>
+      </c>
+      <c r="BP19" s="82">
+        <f t="shared" si="46"/>
+        <v>4.75</v>
+      </c>
+      <c r="BQ19" s="82">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="BR19" s="82">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BK19" s="80">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BL19" s="16">
+      <c r="BS19" s="82">
+        <f t="shared" ref="BS19:BT19" si="47">TEXT(MAX(0,MIN($BM19,BS$7)-MAX($BL19,BS$6)),"h:mm")*24</f>
+        <v>0</v>
+      </c>
+      <c r="BT19" s="83">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="BU19" s="82">
         <f t="shared" si="18"/>
-        <v>0.375</v>
-      </c>
-      <c r="BM19" s="31">
+        <v>7.75</v>
+      </c>
+      <c r="BV19" s="82">
         <f t="shared" si="19"/>
-        <v>0.7395833333321207</v>
-      </c>
-      <c r="BN19" s="81">
-        <f t="shared" ref="BN19:BQ19" si="59">TEXT(MAX(0,MIN($BM19,BN$7)-MAX($BL19,BN$6)),"h:mm")*24</f>
-        <v>3</v>
-      </c>
-      <c r="BO19" s="82">
-        <f t="shared" si="59"/>
-        <v>1</v>
-      </c>
-      <c r="BP19" s="82">
-        <f t="shared" si="59"/>
-        <v>4.75</v>
-      </c>
-      <c r="BQ19" s="82">
-        <f t="shared" si="59"/>
-        <v>0</v>
-      </c>
-      <c r="BR19" s="82">
+        <v>0</v>
+      </c>
+      <c r="BW19" s="82">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="BX19" s="82">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="BS19" s="82">
-        <f t="shared" ref="BS19:BT19" si="60">TEXT(MAX(0,MIN($BM19,BS$7)-MAX($BL19,BS$6)),"h:mm")*24</f>
-        <v>0</v>
-      </c>
-      <c r="BT19" s="83">
-        <f t="shared" si="60"/>
-        <v>0</v>
-      </c>
-      <c r="BU19" s="82">
+      <c r="BY19" s="82">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BZ19" s="84">
         <f t="shared" si="23"/>
-        <v>7.75</v>
-      </c>
-      <c r="BV19" s="82">
+        <v>0</v>
+      </c>
+      <c r="CA19" s="84">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="BW19" s="82">
+      <c r="CB19" s="84">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="BX19" s="82">
+      <c r="CC19" s="82">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="BY19" s="82">
+      <c r="CD19" s="11">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BZ19" s="84">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="CA19" s="84">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="CB19" s="84">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CC19" s="82">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="CD19" s="11">
-        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="CE19" s="11"/>
@@ -5030,30 +5055,28 @@
       <c r="L20" s="55"/>
       <c r="M20" s="67">
         <f>IF(E20="","",IF((BO20+BQ20)=0,"",(BO20+BQ20)*60))</f>
-        <v>60</v>
       </c>
       <c r="N20" s="55"/>
       <c r="O20" s="68">
-        <f t="shared" si="58"/>
-        <v>0.3229166666678793</v>
+        <f>IF(E20&lt;&gt;"",IF(BU20&lt;&gt;0,BU20/24,""),"")</f>
       </c>
       <c r="P20" s="26"/>
       <c r="Q20" s="26"/>
       <c r="R20" s="55"/>
       <c r="S20" s="68">
-        <f t="shared" ref="S20:S35" si="61">IF(E20&lt;&gt;"",IF(BY20&lt;&gt;0,BY20/24,""),"")</f>
+        <f>IF(E20&lt;&gt;"",IF(BY20&lt;&gt;0,BY20/24,""),"")</f>
       </c>
       <c r="T20" s="26"/>
       <c r="U20" s="26"/>
       <c r="V20" s="55"/>
       <c r="W20" s="68">
-        <f t="shared" si="8"/>
+        <f>IF(E20&lt;&gt;"",IF(BS20&lt;&gt;0,BS20/24,""),"")</f>
       </c>
       <c r="X20" s="26"/>
       <c r="Y20" s="26"/>
       <c r="Z20" s="55"/>
       <c r="AA20" s="68">
-        <f t="shared" si="9"/>
+        <f>IF(E20&lt;&gt;"",IF(CA20&lt;&gt;0,CA20/24,""),"")</f>
       </c>
       <c r="AB20" s="26"/>
       <c r="AC20" s="26"/>
@@ -5070,7 +5093,7 @@
       <c r="AN20" s="72"/>
       <c r="AO20" s="55"/>
       <c r="AP20" s="73">
-        <f t="shared" si="10"/>
+        <f>IF(OR(AJ20&lt;&gt;"",AN20&lt;&gt;"",(BV20+BW20)&lt;&gt;0),IF(CD20=1,"","要"),IF(OR(S20&lt;&gt;"",W20&lt;&gt;"",AA20&lt;&gt;""),"申",""))</f>
       </c>
       <c r="AQ20" s="54" t="s">
         <v>83</v>
@@ -5088,19 +5111,19 @@
       <c r="BB20" s="55"/>
       <c r="BC20" s="3"/>
       <c r="BD20" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BE20" s="11">
-        <f t="shared" ref="BE20:BE39" si="62">$A$3</f>
+        <f t="shared" ref="BE20:BE39" si="48">$A$3</f>
         <v>2026</v>
       </c>
       <c r="BF20" s="11">
-        <f t="shared" ref="BF20:BF39" si="63">IF($B$5=$O$5,IF($B$5&lt;$I$3,$B$5+1,$B$5),$I$3)</f>
+        <f t="shared" ref="BF20:BF39" si="49">IF($B$5=$O$5,IF($B$5&lt;$I$3,$B$5+1,$B$5),$I$3)</f>
         <v>9</v>
       </c>
       <c r="BG20" s="11" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>2026/9/1</v>
       </c>
       <c r="BH20" s="79">
@@ -5108,91 +5131,91 @@
         <v>1</v>
       </c>
       <c r="BI20" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ20" s="11">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BK20" s="80">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BL20" s="16">
+        <f t="shared" si="13"/>
+        <v>0.375</v>
+      </c>
+      <c r="BM20" s="31">
+        <f t="shared" si="14"/>
+        <v>0.7395833333321207</v>
+      </c>
+      <c r="BN20" s="81">
+        <f t="shared" ref="BN20:BQ20" si="50">TEXT(MAX(0,MIN($BM20,BN$7)-MAX($BL20,BN$6)),"h:mm")*24</f>
+        <v>3</v>
+      </c>
+      <c r="BO20" s="82">
+        <f t="shared" si="50"/>
+        <v>1</v>
+      </c>
+      <c r="BP20" s="82">
+        <f t="shared" si="50"/>
+        <v>4.75</v>
+      </c>
+      <c r="BQ20" s="82">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="BR20" s="82">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BK20" s="80">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BL20" s="16">
+      <c r="BS20" s="82">
+        <f t="shared" ref="BS20:BT20" si="51">TEXT(MAX(0,MIN($BM20,BS$7)-MAX($BL20,BS$6)),"h:mm")*24</f>
+        <v>0</v>
+      </c>
+      <c r="BT20" s="83">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="BU20" s="82">
         <f t="shared" si="18"/>
-        <v>0.375</v>
-      </c>
-      <c r="BM20" s="31">
+        <v>7.75</v>
+      </c>
+      <c r="BV20" s="82">
         <f t="shared" si="19"/>
-        <v>0.7395833333321207</v>
-      </c>
-      <c r="BN20" s="81">
-        <f t="shared" ref="BN20:BQ20" si="64">TEXT(MAX(0,MIN($BM20,BN$7)-MAX($BL20,BN$6)),"h:mm")*24</f>
-        <v>3</v>
-      </c>
-      <c r="BO20" s="82">
-        <f t="shared" si="64"/>
-        <v>1</v>
-      </c>
-      <c r="BP20" s="82">
-        <f t="shared" si="64"/>
-        <v>4.75</v>
-      </c>
-      <c r="BQ20" s="82">
-        <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="BR20" s="82">
+        <v>0</v>
+      </c>
+      <c r="BW20" s="82">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="BX20" s="82">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="BS20" s="82">
-        <f t="shared" ref="BS20:BT20" si="65">TEXT(MAX(0,MIN($BM20,BS$7)-MAX($BL20,BS$6)),"h:mm")*24</f>
-        <v>0</v>
-      </c>
-      <c r="BT20" s="83">
-        <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="BU20" s="82">
+      <c r="BY20" s="82">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BZ20" s="84">
         <f t="shared" si="23"/>
-        <v>7.75</v>
-      </c>
-      <c r="BV20" s="82">
+        <v>0</v>
+      </c>
+      <c r="CA20" s="84">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="BW20" s="82">
+      <c r="CB20" s="84">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="BX20" s="82">
+      <c r="CC20" s="82">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="BY20" s="82">
+      <c r="CD20" s="11">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BZ20" s="84">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="CA20" s="84">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="CB20" s="84">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CC20" s="82">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="CD20" s="11">
-        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="CE20" s="11"/>
@@ -5223,30 +5246,28 @@
       <c r="L21" s="55"/>
       <c r="M21" s="67">
         <f>IF(E21="","",IF((BO21+BQ21)=0,"",(BO21+BQ21)*60))</f>
-        <v>60</v>
       </c>
       <c r="N21" s="55"/>
       <c r="O21" s="68">
-        <f t="shared" si="58"/>
-        <v>0.3229166666678793</v>
+        <f>IF(E21&lt;&gt;"",IF(BU21&lt;&gt;0,BU21/24,""),"")</f>
       </c>
       <c r="P21" s="26"/>
       <c r="Q21" s="26"/>
       <c r="R21" s="55"/>
       <c r="S21" s="68">
-        <f t="shared" si="61"/>
+        <f>IF(E21&lt;&gt;"",IF(BY21&lt;&gt;0,BY21/24,""),"")</f>
       </c>
       <c r="T21" s="26"/>
       <c r="U21" s="26"/>
       <c r="V21" s="55"/>
       <c r="W21" s="68">
-        <f t="shared" si="8"/>
+        <f>IF(E21&lt;&gt;"",IF(BS21&lt;&gt;0,BS21/24,""),"")</f>
       </c>
       <c r="X21" s="26"/>
       <c r="Y21" s="26"/>
       <c r="Z21" s="55"/>
       <c r="AA21" s="68">
-        <f t="shared" si="9"/>
+        <f>IF(E21&lt;&gt;"",IF(CA21&lt;&gt;0,CA21/24,""),"")</f>
       </c>
       <c r="AB21" s="26"/>
       <c r="AC21" s="26"/>
@@ -5263,7 +5284,7 @@
       <c r="AN21" s="72"/>
       <c r="AO21" s="55"/>
       <c r="AP21" s="73">
-        <f t="shared" si="10"/>
+        <f>IF(OR(AJ21&lt;&gt;"",AN21&lt;&gt;"",(BV21+BW21)&lt;&gt;0),IF(CD21=1,"","要"),IF(OR(S21&lt;&gt;"",W21&lt;&gt;"",AA21&lt;&gt;""),"申",""))</f>
       </c>
       <c r="AQ21" s="94" t="s">
         <v>84</v>
@@ -5281,19 +5302,19 @@
       <c r="BB21" s="37"/>
       <c r="BC21" s="3"/>
       <c r="BD21" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BE21" s="11">
-        <f t="shared" si="62"/>
+        <f t="shared" si="48"/>
         <v>2026</v>
       </c>
       <c r="BF21" s="11">
-        <f t="shared" si="63"/>
+        <f t="shared" si="49"/>
         <v>9</v>
       </c>
       <c r="BG21" s="11" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>2026/9/2</v>
       </c>
       <c r="BH21" s="79">
@@ -5301,91 +5322,91 @@
         <v>1</v>
       </c>
       <c r="BI21" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ21" s="11">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BK21" s="80">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BL21" s="16">
+        <f t="shared" si="13"/>
+        <v>0.375</v>
+      </c>
+      <c r="BM21" s="31">
+        <f t="shared" si="14"/>
+        <v>0.7395833333321207</v>
+      </c>
+      <c r="BN21" s="81">
+        <f t="shared" ref="BN21:BQ21" si="52">TEXT(MAX(0,MIN($BM21,BN$7)-MAX($BL21,BN$6)),"h:mm")*24</f>
+        <v>3</v>
+      </c>
+      <c r="BO21" s="82">
+        <f t="shared" si="52"/>
+        <v>1</v>
+      </c>
+      <c r="BP21" s="82">
+        <f t="shared" si="52"/>
+        <v>4.75</v>
+      </c>
+      <c r="BQ21" s="82">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="BR21" s="82">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BK21" s="80">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BL21" s="16">
+      <c r="BS21" s="82">
+        <f t="shared" ref="BS21:BT21" si="53">TEXT(MAX(0,MIN($BM21,BS$7)-MAX($BL21,BS$6)),"h:mm")*24</f>
+        <v>0</v>
+      </c>
+      <c r="BT21" s="83">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="BU21" s="82">
         <f t="shared" si="18"/>
-        <v>0.375</v>
-      </c>
-      <c r="BM21" s="31">
+        <v>7.75</v>
+      </c>
+      <c r="BV21" s="82">
         <f t="shared" si="19"/>
-        <v>0.7395833333321207</v>
-      </c>
-      <c r="BN21" s="81">
-        <f t="shared" ref="BN21:BQ21" si="66">TEXT(MAX(0,MIN($BM21,BN$7)-MAX($BL21,BN$6)),"h:mm")*24</f>
-        <v>3</v>
-      </c>
-      <c r="BO21" s="82">
-        <f t="shared" si="66"/>
-        <v>1</v>
-      </c>
-      <c r="BP21" s="82">
-        <f t="shared" si="66"/>
-        <v>4.75</v>
-      </c>
-      <c r="BQ21" s="82">
-        <f t="shared" si="66"/>
-        <v>0</v>
-      </c>
-      <c r="BR21" s="82">
+        <v>0</v>
+      </c>
+      <c r="BW21" s="82">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="BX21" s="82">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="BS21" s="82">
-        <f t="shared" ref="BS21:BT21" si="67">TEXT(MAX(0,MIN($BM21,BS$7)-MAX($BL21,BS$6)),"h:mm")*24</f>
-        <v>0</v>
-      </c>
-      <c r="BT21" s="83">
-        <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="BU21" s="82">
+      <c r="BY21" s="82">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BZ21" s="84">
         <f t="shared" si="23"/>
-        <v>7.75</v>
-      </c>
-      <c r="BV21" s="82">
+        <v>0</v>
+      </c>
+      <c r="CA21" s="84">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="BW21" s="82">
+      <c r="CB21" s="84">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="BX21" s="82">
+      <c r="CC21" s="82">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="BY21" s="82">
+      <c r="CD21" s="11">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BZ21" s="84">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="CA21" s="84">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="CB21" s="84">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CC21" s="82">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="CD21" s="11">
-        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="CE21" s="11"/>
@@ -5415,31 +5436,29 @@
       <c r="K22" s="66"/>
       <c r="L22" s="55"/>
       <c r="M22" s="67">
-        <f t="shared" ref="M22" si="68">IF(E22="","",IF((BO22+BQ22)=0,"",(BO22+BQ22)*60))</f>
-        <v>60</v>
+        <f>IF(E22="","",IF((BO22+BQ22)=0,"",(BO22+BQ22)*60))</f>
       </c>
       <c r="N22" s="55"/>
       <c r="O22" s="68">
-        <f t="shared" si="58"/>
-        <v>0.3229166666678793</v>
+        <f>IF(E22&lt;&gt;"",IF(BU22&lt;&gt;0,BU22/24,""),"")</f>
       </c>
       <c r="P22" s="26"/>
       <c r="Q22" s="26"/>
       <c r="R22" s="55"/>
       <c r="S22" s="68">
-        <f t="shared" si="61"/>
+        <f>IF(E22&lt;&gt;"",IF(BY22&lt;&gt;0,BY22/24,""),"")</f>
       </c>
       <c r="T22" s="26"/>
       <c r="U22" s="26"/>
       <c r="V22" s="55"/>
       <c r="W22" s="68">
-        <f t="shared" si="8"/>
+        <f>IF(E22&lt;&gt;"",IF(BS22&lt;&gt;0,BS22/24,""),"")</f>
       </c>
       <c r="X22" s="26"/>
       <c r="Y22" s="26"/>
       <c r="Z22" s="55"/>
       <c r="AA22" s="68">
-        <f t="shared" si="9"/>
+        <f>IF(E22&lt;&gt;"",IF(CA22&lt;&gt;0,CA22/24,""),"")</f>
       </c>
       <c r="AB22" s="26"/>
       <c r="AC22" s="26"/>
@@ -5456,7 +5475,7 @@
       <c r="AN22" s="72"/>
       <c r="AO22" s="55"/>
       <c r="AP22" s="73">
-        <f t="shared" si="10"/>
+        <f>IF(OR(AJ22&lt;&gt;"",AN22&lt;&gt;"",(BV22+BW22)&lt;&gt;0),IF(CD22=1,"","要"),IF(OR(S22&lt;&gt;"",W22&lt;&gt;"",AA22&lt;&gt;""),"申",""))</f>
       </c>
       <c r="AQ22" s="47"/>
       <c r="AR22" s="14"/>
@@ -5472,19 +5491,19 @@
       <c r="BB22" s="48"/>
       <c r="BC22" s="3"/>
       <c r="BD22" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BE22" s="11">
-        <f t="shared" si="62"/>
+        <f t="shared" si="48"/>
         <v>2026</v>
       </c>
       <c r="BF22" s="11">
-        <f t="shared" si="63"/>
+        <f t="shared" si="49"/>
         <v>9</v>
       </c>
       <c r="BG22" s="11" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>2026/9/3</v>
       </c>
       <c r="BH22" s="79">
@@ -5492,91 +5511,91 @@
         <v>1</v>
       </c>
       <c r="BI22" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ22" s="11">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BK22" s="80">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BL22" s="16">
+        <f t="shared" si="13"/>
+        <v>0.375</v>
+      </c>
+      <c r="BM22" s="31">
+        <f t="shared" si="14"/>
+        <v>0.7395833333321207</v>
+      </c>
+      <c r="BN22" s="81">
+        <f t="shared" ref="BN22:BQ22" si="54">TEXT(MAX(0,MIN($BM22,BN$7)-MAX($BL22,BN$6)),"h:mm")*24</f>
+        <v>3</v>
+      </c>
+      <c r="BO22" s="82">
+        <f t="shared" si="54"/>
+        <v>1</v>
+      </c>
+      <c r="BP22" s="82">
+        <f t="shared" si="54"/>
+        <v>4.75</v>
+      </c>
+      <c r="BQ22" s="82">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="BR22" s="82">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BK22" s="80">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BL22" s="16">
+      <c r="BS22" s="82">
+        <f t="shared" ref="BS22:BT22" si="55">TEXT(MAX(0,MIN($BM22,BS$7)-MAX($BL22,BS$6)),"h:mm")*24</f>
+        <v>0</v>
+      </c>
+      <c r="BT22" s="83">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="BU22" s="82">
         <f t="shared" si="18"/>
-        <v>0.375</v>
-      </c>
-      <c r="BM22" s="31">
+        <v>7.75</v>
+      </c>
+      <c r="BV22" s="82">
         <f t="shared" si="19"/>
-        <v>0.7395833333321207</v>
-      </c>
-      <c r="BN22" s="81">
-        <f t="shared" ref="BN22:BQ22" si="69">TEXT(MAX(0,MIN($BM22,BN$7)-MAX($BL22,BN$6)),"h:mm")*24</f>
-        <v>3</v>
-      </c>
-      <c r="BO22" s="82">
-        <f t="shared" si="69"/>
-        <v>1</v>
-      </c>
-      <c r="BP22" s="82">
-        <f t="shared" si="69"/>
-        <v>4.75</v>
-      </c>
-      <c r="BQ22" s="82">
-        <f t="shared" si="69"/>
-        <v>0</v>
-      </c>
-      <c r="BR22" s="82">
+        <v>0</v>
+      </c>
+      <c r="BW22" s="82">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="BX22" s="82">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="BS22" s="82">
-        <f t="shared" ref="BS22:BT22" si="70">TEXT(MAX(0,MIN($BM22,BS$7)-MAX($BL22,BS$6)),"h:mm")*24</f>
-        <v>0</v>
-      </c>
-      <c r="BT22" s="83">
-        <f t="shared" si="70"/>
-        <v>0</v>
-      </c>
-      <c r="BU22" s="82">
+      <c r="BY22" s="82">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BZ22" s="84">
         <f t="shared" si="23"/>
-        <v>7.75</v>
-      </c>
-      <c r="BV22" s="82">
+        <v>0</v>
+      </c>
+      <c r="CA22" s="84">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="BW22" s="82">
+      <c r="CB22" s="84">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="BX22" s="82">
+      <c r="CC22" s="82">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="BY22" s="82">
+      <c r="CD22" s="11">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BZ22" s="84">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="CA22" s="84">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="CB22" s="84">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CC22" s="82">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="CD22" s="11">
-        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="CE22" s="11"/>
@@ -5606,30 +5625,30 @@
       <c r="K23" s="66"/>
       <c r="L23" s="55"/>
       <c r="M23" s="67">
-        <f t="shared" ref="M23" si="71">IF(E23="","",IF((BO23+BQ23)=0,"",(BO23+BQ23)*60))</f>
-        <v>60</v>
+        <f>IF(E23="","",IF((BO23+BQ23)=0,"",(BO23+BQ23)*60))</f>
       </c>
       <c r="N23" s="55"/>
       <c r="O23" s="68">
-        <f t="shared" si="58"/>
-        <v>0.3229166666678793</v>
+        <f>IF(E23&lt;&gt;"",IF(BU23&lt;&gt;0,BU23/24,""),"")</f>
       </c>
       <c r="P23" s="26"/>
       <c r="Q23" s="26"/>
       <c r="R23" s="55"/>
       <c r="S23" s="68">
-        <f t="shared" si="61"/>
+        <f>IF(E23&lt;&gt;"",IF(BY23&lt;&gt;0,BY23/24,""),"")</f>
       </c>
       <c r="T23" s="26"/>
       <c r="U23" s="26"/>
       <c r="V23" s="55"/>
       <c r="W23" s="68">
-        <f t="shared" si="8"/>
+        <f>IF(E23&lt;&gt;"",IF(BS23&lt;&gt;0,BS23/24,""),"")</f>
       </c>
       <c r="X23" s="26"/>
       <c r="Y23" s="26"/>
       <c r="Z23" s="55"/>
-      <c r="AA23" s="68"/>
+      <c r="AA23" s="68">
+        <f>IF(E23&lt;&gt;"",IF(CA23&lt;&gt;0,CA23/24,""),"")</f>
+      </c>
       <c r="AB23" s="26"/>
       <c r="AC23" s="26"/>
       <c r="AD23" s="55"/>
@@ -5645,7 +5664,7 @@
       <c r="AN23" s="72"/>
       <c r="AO23" s="55"/>
       <c r="AP23" s="73">
-        <f t="shared" si="10"/>
+        <f>IF(OR(AJ23&lt;&gt;"",AN23&lt;&gt;"",(BV23+BW23)&lt;&gt;0),IF(CD23=1,"","要"),IF(OR(S23&lt;&gt;"",W23&lt;&gt;"",AA23&lt;&gt;""),"申",""))</f>
       </c>
       <c r="AQ23" s="74" t="s">
         <v>23</v>
@@ -5665,19 +5684,19 @@
       <c r="BB23" s="55"/>
       <c r="BC23" s="3"/>
       <c r="BD23" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BE23" s="11">
-        <f t="shared" si="62"/>
+        <f t="shared" si="48"/>
         <v>2026</v>
       </c>
       <c r="BF23" s="11">
-        <f t="shared" si="63"/>
+        <f t="shared" si="49"/>
         <v>9</v>
       </c>
       <c r="BG23" s="11" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>2026/9/4</v>
       </c>
       <c r="BH23" s="79">
@@ -5685,91 +5704,91 @@
         <v>1</v>
       </c>
       <c r="BI23" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ23" s="11">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BK23" s="80">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BL23" s="16">
+        <f t="shared" si="13"/>
+        <v>0.375</v>
+      </c>
+      <c r="BM23" s="31">
+        <f t="shared" si="14"/>
+        <v>0.7395833333321207</v>
+      </c>
+      <c r="BN23" s="81">
+        <f t="shared" ref="BN23:BQ23" si="56">TEXT(MAX(0,MIN($BM23,BN$7)-MAX($BL23,BN$6)),"h:mm")*24</f>
+        <v>3</v>
+      </c>
+      <c r="BO23" s="82">
+        <f t="shared" si="56"/>
+        <v>1</v>
+      </c>
+      <c r="BP23" s="82">
+        <f t="shared" si="56"/>
+        <v>4.75</v>
+      </c>
+      <c r="BQ23" s="82">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+      <c r="BR23" s="82">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BK23" s="80">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BL23" s="16">
+      <c r="BS23" s="82">
+        <f t="shared" ref="BS23:BT23" si="57">TEXT(MAX(0,MIN($BM23,BS$7)-MAX($BL23,BS$6)),"h:mm")*24</f>
+        <v>0</v>
+      </c>
+      <c r="BT23" s="83">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
+      <c r="BU23" s="82">
         <f t="shared" si="18"/>
-        <v>0.375</v>
-      </c>
-      <c r="BM23" s="31">
+        <v>7.75</v>
+      </c>
+      <c r="BV23" s="82">
         <f t="shared" si="19"/>
-        <v>0.7395833333321207</v>
-      </c>
-      <c r="BN23" s="81">
-        <f t="shared" ref="BN23:BQ23" si="72">TEXT(MAX(0,MIN($BM23,BN$7)-MAX($BL23,BN$6)),"h:mm")*24</f>
-        <v>3</v>
-      </c>
-      <c r="BO23" s="82">
-        <f t="shared" si="72"/>
-        <v>1</v>
-      </c>
-      <c r="BP23" s="82">
-        <f t="shared" si="72"/>
-        <v>4.75</v>
-      </c>
-      <c r="BQ23" s="82">
-        <f t="shared" si="72"/>
-        <v>0</v>
-      </c>
-      <c r="BR23" s="82">
+        <v>0</v>
+      </c>
+      <c r="BW23" s="82">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="BX23" s="82">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="BS23" s="82">
-        <f t="shared" ref="BS23:BT23" si="73">TEXT(MAX(0,MIN($BM23,BS$7)-MAX($BL23,BS$6)),"h:mm")*24</f>
-        <v>0</v>
-      </c>
-      <c r="BT23" s="83">
-        <f t="shared" si="73"/>
-        <v>0</v>
-      </c>
-      <c r="BU23" s="82">
+      <c r="BY23" s="82">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BZ23" s="84">
         <f t="shared" si="23"/>
-        <v>7.75</v>
-      </c>
-      <c r="BV23" s="82">
+        <v>0</v>
+      </c>
+      <c r="CA23" s="84">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="BW23" s="82">
+      <c r="CB23" s="84">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="BX23" s="82">
+      <c r="CC23" s="82">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="BY23" s="82">
+      <c r="CD23" s="11">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BZ23" s="84">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="CA23" s="84">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="CB23" s="84">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CC23" s="82">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="CD23" s="11">
-        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="CE23" s="11"/>
@@ -5798,21 +5817,31 @@
       <c r="J24" s="65"/>
       <c r="K24" s="66"/>
       <c r="L24" s="55"/>
-      <c r="M24" s="67"/>
+      <c r="M24" s="67">
+        <f>IF(E24="","",IF((BO24+BQ24)=0,"",(BO24+BQ24)*60))</f>
+      </c>
       <c r="N24" s="55"/>
-      <c r="O24" s="68"/>
+      <c r="O24" s="68">
+        <f>IF(E24&lt;&gt;"",IF(BU24&lt;&gt;0,BU24/24,""),"")</f>
+      </c>
       <c r="P24" s="26"/>
       <c r="Q24" s="26"/>
       <c r="R24" s="55"/>
-      <c r="S24" s="68"/>
+      <c r="S24" s="68">
+        <f>IF(E24&lt;&gt;"",IF(BY24&lt;&gt;0,BY24/24,""),"")</f>
+      </c>
       <c r="T24" s="26"/>
       <c r="U24" s="26"/>
       <c r="V24" s="55"/>
-      <c r="W24" s="68"/>
+      <c r="W24" s="68">
+        <f>IF(E24&lt;&gt;"",IF(BS24&lt;&gt;0,BS24/24,""),"")</f>
+      </c>
       <c r="X24" s="26"/>
       <c r="Y24" s="26"/>
       <c r="Z24" s="55"/>
-      <c r="AA24" s="68"/>
+      <c r="AA24" s="68">
+        <f>IF(E24&lt;&gt;"",IF(CA24&lt;&gt;0,CA24/24,""),"")</f>
+      </c>
       <c r="AB24" s="26"/>
       <c r="AC24" s="26"/>
       <c r="AD24" s="55"/>
@@ -5828,7 +5857,7 @@
       <c r="AN24" s="72"/>
       <c r="AO24" s="55"/>
       <c r="AP24" s="73">
-        <f t="shared" si="10"/>
+        <f>IF(OR(AJ24&lt;&gt;"",AN24&lt;&gt;"",(BV24+BW24)&lt;&gt;0),IF(CD24=1,"","要"),IF(OR(S24&lt;&gt;"",W24&lt;&gt;"",AA24&lt;&gt;""),"申",""))</f>
       </c>
       <c r="AQ24" s="54" t="s">
         <v>86</v>
@@ -5850,19 +5879,19 @@
       <c r="BB24" s="78"/>
       <c r="BC24" s="3"/>
       <c r="BD24" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BE24" s="11">
-        <f t="shared" si="62"/>
+        <f t="shared" si="48"/>
         <v>2026</v>
       </c>
       <c r="BF24" s="11">
-        <f t="shared" si="63"/>
+        <f t="shared" si="49"/>
         <v>9</v>
       </c>
       <c r="BG24" s="11" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>2026/9/5</v>
       </c>
       <c r="BH24" s="79">
@@ -5870,91 +5899,91 @@
         <v>0</v>
       </c>
       <c r="BI24" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ24" s="11">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BK24" s="80">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BL24" s="16">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="BM24" s="31">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="BN24" s="81">
+        <f t="shared" ref="BN24:BQ24" si="58">TEXT(MAX(0,MIN($BM24,BN$7)-MAX($BL24,BN$6)),"h:mm")*24</f>
+        <v>0</v>
+      </c>
+      <c r="BO24" s="82">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="BP24" s="82">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="BQ24" s="82">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="BR24" s="82">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BK24" s="80">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BL24" s="16">
+      <c r="BS24" s="82">
+        <f t="shared" ref="BS24:BT24" si="59">TEXT(MAX(0,MIN($BM24,BS$7)-MAX($BL24,BS$6)),"h:mm")*24</f>
+        <v>0</v>
+      </c>
+      <c r="BT24" s="83">
+        <f t="shared" si="59"/>
+        <v>0</v>
+      </c>
+      <c r="BU24" s="82">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BM24" s="31">
+      <c r="BV24" s="82">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="BN24" s="81">
-        <f t="shared" ref="BN24:BQ24" si="74">TEXT(MAX(0,MIN($BM24,BN$7)-MAX($BL24,BN$6)),"h:mm")*24</f>
-        <v>0</v>
-      </c>
-      <c r="BO24" s="82">
-        <f t="shared" si="74"/>
-        <v>0</v>
-      </c>
-      <c r="BP24" s="82">
-        <f t="shared" si="74"/>
-        <v>0</v>
-      </c>
-      <c r="BQ24" s="82">
-        <f t="shared" si="74"/>
-        <v>0</v>
-      </c>
-      <c r="BR24" s="82">
+      <c r="BW24" s="82">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="BX24" s="82">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="BS24" s="82">
-        <f t="shared" ref="BS24:BT24" si="75">TEXT(MAX(0,MIN($BM24,BS$7)-MAX($BL24,BS$6)),"h:mm")*24</f>
-        <v>0</v>
-      </c>
-      <c r="BT24" s="83">
-        <f t="shared" si="75"/>
-        <v>0</v>
-      </c>
-      <c r="BU24" s="82">
+      <c r="BY24" s="82">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BZ24" s="84">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="BV24" s="82">
+      <c r="CA24" s="84">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="BW24" s="82">
+      <c r="CB24" s="84">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="BX24" s="82">
+      <c r="CC24" s="82">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="BY24" s="82">
+      <c r="CD24" s="11">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BZ24" s="84">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="CA24" s="84">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="CB24" s="84">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CC24" s="82">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="CD24" s="11">
-        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="CE24" s="11"/>
@@ -5983,21 +6012,31 @@
       <c r="J25" s="65"/>
       <c r="K25" s="66"/>
       <c r="L25" s="55"/>
-      <c r="M25" s="67"/>
+      <c r="M25" s="67">
+        <f>IF(E25="","",IF((BO25+BQ25)=0,"",(BO25+BQ25)*60))</f>
+      </c>
       <c r="N25" s="55"/>
-      <c r="O25" s="68"/>
+      <c r="O25" s="68">
+        <f>IF(E25&lt;&gt;"",IF(BU25&lt;&gt;0,BU25/24,""),"")</f>
+      </c>
       <c r="P25" s="26"/>
       <c r="Q25" s="26"/>
       <c r="R25" s="55"/>
-      <c r="S25" s="68"/>
+      <c r="S25" s="68">
+        <f>IF(E25&lt;&gt;"",IF(BY25&lt;&gt;0,BY25/24,""),"")</f>
+      </c>
       <c r="T25" s="26"/>
       <c r="U25" s="26"/>
       <c r="V25" s="55"/>
-      <c r="W25" s="68"/>
+      <c r="W25" s="68">
+        <f>IF(E25&lt;&gt;"",IF(BS25&lt;&gt;0,BS25/24,""),"")</f>
+      </c>
       <c r="X25" s="26"/>
       <c r="Y25" s="26"/>
       <c r="Z25" s="55"/>
-      <c r="AA25" s="68"/>
+      <c r="AA25" s="68">
+        <f>IF(E25&lt;&gt;"",IF(CA25&lt;&gt;0,CA25/24,""),"")</f>
+      </c>
       <c r="AB25" s="26"/>
       <c r="AC25" s="26"/>
       <c r="AD25" s="55"/>
@@ -6013,7 +6052,7 @@
       <c r="AN25" s="72"/>
       <c r="AO25" s="55"/>
       <c r="AP25" s="73">
-        <f t="shared" si="10"/>
+        <f>IF(OR(AJ25&lt;&gt;"",AN25&lt;&gt;"",(BV25+BW25)&lt;&gt;0),IF(CD25=1,"","要"),IF(OR(S25&lt;&gt;"",W25&lt;&gt;"",AA25&lt;&gt;""),"申",""))</f>
       </c>
       <c r="AQ25" s="94" t="s">
         <v>64</v>
@@ -6031,19 +6070,19 @@
       <c r="BB25" s="37"/>
       <c r="BC25" s="3"/>
       <c r="BD25" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BE25" s="11">
-        <f t="shared" si="62"/>
+        <f t="shared" si="48"/>
         <v>2026</v>
       </c>
       <c r="BF25" s="11">
-        <f t="shared" si="63"/>
+        <f t="shared" si="49"/>
         <v>9</v>
       </c>
       <c r="BG25" s="11" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>2026/9/6</v>
       </c>
       <c r="BH25" s="79">
@@ -6051,91 +6090,91 @@
         <v>0</v>
       </c>
       <c r="BI25" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ25" s="11">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BK25" s="80">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BL25" s="16">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="BM25" s="31">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="BN25" s="81">
+        <f t="shared" ref="BN25:BQ25" si="60">TEXT(MAX(0,MIN($BM25,BN$7)-MAX($BL25,BN$6)),"h:mm")*24</f>
+        <v>0</v>
+      </c>
+      <c r="BO25" s="82">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="BP25" s="82">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="BQ25" s="82">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="BR25" s="82">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BK25" s="80">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BL25" s="16">
+      <c r="BS25" s="82">
+        <f t="shared" ref="BS25:BT25" si="61">TEXT(MAX(0,MIN($BM25,BS$7)-MAX($BL25,BS$6)),"h:mm")*24</f>
+        <v>0</v>
+      </c>
+      <c r="BT25" s="83">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="BU25" s="82">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BM25" s="31">
+      <c r="BV25" s="82">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="BN25" s="81">
-        <f t="shared" ref="BN25:BQ25" si="76">TEXT(MAX(0,MIN($BM25,BN$7)-MAX($BL25,BN$6)),"h:mm")*24</f>
-        <v>0</v>
-      </c>
-      <c r="BO25" s="82">
-        <f t="shared" si="76"/>
-        <v>0</v>
-      </c>
-      <c r="BP25" s="82">
-        <f t="shared" si="76"/>
-        <v>0</v>
-      </c>
-      <c r="BQ25" s="82">
-        <f t="shared" si="76"/>
-        <v>0</v>
-      </c>
-      <c r="BR25" s="82">
+      <c r="BW25" s="82">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="BX25" s="82">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="BS25" s="82">
-        <f t="shared" ref="BS25:BT25" si="77">TEXT(MAX(0,MIN($BM25,BS$7)-MAX($BL25,BS$6)),"h:mm")*24</f>
-        <v>0</v>
-      </c>
-      <c r="BT25" s="83">
-        <f t="shared" si="77"/>
-        <v>0</v>
-      </c>
-      <c r="BU25" s="82">
+      <c r="BY25" s="82">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BZ25" s="84">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="BV25" s="82">
+      <c r="CA25" s="84">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="BW25" s="82">
+      <c r="CB25" s="84">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="BX25" s="82">
+      <c r="CC25" s="82">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="BY25" s="82">
+      <c r="CD25" s="11">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BZ25" s="84">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="CA25" s="84">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="CB25" s="84">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CC25" s="82">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="CD25" s="11">
-        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="CE25" s="11"/>
@@ -6166,30 +6205,28 @@
       <c r="L26" s="55"/>
       <c r="M26" s="67">
         <f>IF(E26="","",IF((BO26+BQ26)=0,"",(BO26+BQ26)*60))</f>
-        <v>60</v>
       </c>
       <c r="N26" s="55"/>
       <c r="O26" s="68">
-        <f t="shared" ref="O26" si="78">IF(E26&lt;&gt;"",IF(BU26&lt;&gt;0,BU26/24,""),"")</f>
-        <v>0.3229166666678793</v>
+        <f>IF(E26&lt;&gt;"",IF(BU26&lt;&gt;0,BU26/24,""),"")</f>
       </c>
       <c r="P26" s="26"/>
       <c r="Q26" s="26"/>
       <c r="R26" s="55"/>
       <c r="S26" s="68">
-        <f t="shared" si="61"/>
+        <f>IF(E26&lt;&gt;"",IF(BY26&lt;&gt;0,BY26/24,""),"")</f>
       </c>
       <c r="T26" s="26"/>
       <c r="U26" s="26"/>
       <c r="V26" s="55"/>
       <c r="W26" s="68">
-        <f t="shared" si="8"/>
+        <f>IF(E26&lt;&gt;"",IF(BS26&lt;&gt;0,BS26/24,""),"")</f>
       </c>
       <c r="X26" s="26"/>
       <c r="Y26" s="26"/>
       <c r="Z26" s="55"/>
       <c r="AA26" s="68">
-        <f t="shared" ref="AA26:AA35" si="79">IF(E26&lt;&gt;"",IF(CA26&lt;&gt;0,CA26/24,""),"")</f>
+        <f>IF(E26&lt;&gt;"",IF(CA26&lt;&gt;0,CA26/24,""),"")</f>
       </c>
       <c r="AB26" s="26"/>
       <c r="AC26" s="26"/>
@@ -6206,7 +6243,7 @@
       <c r="AN26" s="72"/>
       <c r="AO26" s="55"/>
       <c r="AP26" s="73">
-        <f t="shared" si="10"/>
+        <f>IF(OR(AJ26&lt;&gt;"",AN26&lt;&gt;"",(BV26+BW26)&lt;&gt;0),IF(CD26=1,"","要"),IF(OR(S26&lt;&gt;"",W26&lt;&gt;"",AA26&lt;&gt;""),"申",""))</f>
       </c>
       <c r="AQ26" s="47"/>
       <c r="AR26" s="14"/>
@@ -6222,19 +6259,19 @@
       <c r="BB26" s="48"/>
       <c r="BC26" s="3"/>
       <c r="BD26" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BE26" s="11">
-        <f t="shared" si="62"/>
+        <f t="shared" si="48"/>
         <v>2026</v>
       </c>
       <c r="BF26" s="11">
-        <f t="shared" si="63"/>
+        <f t="shared" si="49"/>
         <v>9</v>
       </c>
       <c r="BG26" s="11" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>2026/9/7</v>
       </c>
       <c r="BH26" s="79">
@@ -6242,91 +6279,91 @@
         <v>1</v>
       </c>
       <c r="BI26" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ26" s="11">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BK26" s="80">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BL26" s="16">
+        <f t="shared" si="13"/>
+        <v>0.375</v>
+      </c>
+      <c r="BM26" s="31">
+        <f t="shared" si="14"/>
+        <v>0.7395833333321207</v>
+      </c>
+      <c r="BN26" s="81">
+        <f t="shared" ref="BN26:BQ26" si="62">TEXT(MAX(0,MIN($BM26,BN$7)-MAX($BL26,BN$6)),"h:mm")*24</f>
+        <v>3</v>
+      </c>
+      <c r="BO26" s="82">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+      <c r="BP26" s="82">
+        <f t="shared" si="62"/>
+        <v>4.75</v>
+      </c>
+      <c r="BQ26" s="82">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="BR26" s="82">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BK26" s="80">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BL26" s="16">
+      <c r="BS26" s="82">
+        <f t="shared" ref="BS26:BT26" si="63">TEXT(MAX(0,MIN($BM26,BS$7)-MAX($BL26,BS$6)),"h:mm")*24</f>
+        <v>0</v>
+      </c>
+      <c r="BT26" s="83">
+        <f t="shared" si="63"/>
+        <v>0</v>
+      </c>
+      <c r="BU26" s="82">
         <f t="shared" si="18"/>
-        <v>0.375</v>
-      </c>
-      <c r="BM26" s="31">
+        <v>7.75</v>
+      </c>
+      <c r="BV26" s="82">
         <f t="shared" si="19"/>
-        <v>0.7395833333321207</v>
-      </c>
-      <c r="BN26" s="81">
-        <f t="shared" ref="BN26:BQ26" si="80">TEXT(MAX(0,MIN($BM26,BN$7)-MAX($BL26,BN$6)),"h:mm")*24</f>
-        <v>3</v>
-      </c>
-      <c r="BO26" s="82">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="BP26" s="82">
-        <f t="shared" si="80"/>
-        <v>4.75</v>
-      </c>
-      <c r="BQ26" s="82">
-        <f t="shared" si="80"/>
-        <v>0</v>
-      </c>
-      <c r="BR26" s="82">
+        <v>0</v>
+      </c>
+      <c r="BW26" s="82">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="BX26" s="82">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="BS26" s="82">
-        <f t="shared" ref="BS26:BT26" si="81">TEXT(MAX(0,MIN($BM26,BS$7)-MAX($BL26,BS$6)),"h:mm")*24</f>
-        <v>0</v>
-      </c>
-      <c r="BT26" s="83">
-        <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="BU26" s="82">
+      <c r="BY26" s="82">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BZ26" s="84">
         <f t="shared" si="23"/>
-        <v>7.75</v>
-      </c>
-      <c r="BV26" s="82">
+        <v>0</v>
+      </c>
+      <c r="CA26" s="84">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="BW26" s="82">
+      <c r="CB26" s="84">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="BX26" s="82">
+      <c r="CC26" s="82">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="BY26" s="82">
+      <c r="CD26" s="11">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BZ26" s="84">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="CA26" s="84">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="CB26" s="84">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CC26" s="82">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="CD26" s="11">
-        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="CE26" s="11"/>
@@ -6357,30 +6394,28 @@
       <c r="L27" s="55"/>
       <c r="M27" s="67">
         <f>IF(E27="","",IF((BO27+BQ27)=0,"",(BO27+BQ27)*60))</f>
-        <v>60</v>
       </c>
       <c r="N27" s="55"/>
       <c r="O27" s="68">
-        <f t="shared" ref="O27:O28" si="82">IF(E27&lt;&gt;"",IF(BU27&lt;&gt;0,BU27/24,""),"")</f>
-        <v>0.3229166666678793</v>
+        <f>IF(E27&lt;&gt;"",IF(BU27&lt;&gt;0,BU27/24,""),"")</f>
       </c>
       <c r="P27" s="26"/>
       <c r="Q27" s="26"/>
       <c r="R27" s="55"/>
       <c r="S27" s="68">
-        <f t="shared" si="61"/>
+        <f>IF(E27&lt;&gt;"",IF(BY27&lt;&gt;0,BY27/24,""),"")</f>
       </c>
       <c r="T27" s="26"/>
       <c r="U27" s="26"/>
       <c r="V27" s="55"/>
       <c r="W27" s="68">
-        <f t="shared" si="8"/>
+        <f>IF(E27&lt;&gt;"",IF(BS27&lt;&gt;0,BS27/24,""),"")</f>
       </c>
       <c r="X27" s="26"/>
       <c r="Y27" s="26"/>
       <c r="Z27" s="55"/>
       <c r="AA27" s="68">
-        <f t="shared" si="79"/>
+        <f>IF(E27&lt;&gt;"",IF(CA27&lt;&gt;0,CA27/24,""),"")</f>
       </c>
       <c r="AB27" s="26"/>
       <c r="AC27" s="26"/>
@@ -6397,7 +6432,7 @@
       <c r="AN27" s="72"/>
       <c r="AO27" s="55"/>
       <c r="AP27" s="73">
-        <f t="shared" si="10"/>
+        <f>IF(OR(AJ27&lt;&gt;"",AN27&lt;&gt;"",(BV27+BW27)&lt;&gt;0),IF(CD27=1,"","要"),IF(OR(S27&lt;&gt;"",W27&lt;&gt;"",AA27&lt;&gt;""),"申",""))</f>
       </c>
       <c r="AQ27" s="54" t="s">
         <v>87</v>
@@ -6419,19 +6454,19 @@
       <c r="BB27" s="78"/>
       <c r="BC27" s="3"/>
       <c r="BD27" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BE27" s="11">
-        <f t="shared" si="62"/>
+        <f t="shared" si="48"/>
         <v>2026</v>
       </c>
       <c r="BF27" s="11">
-        <f t="shared" si="63"/>
+        <f t="shared" si="49"/>
         <v>9</v>
       </c>
       <c r="BG27" s="11" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>2026/9/8</v>
       </c>
       <c r="BH27" s="79">
@@ -6439,91 +6474,91 @@
         <v>1</v>
       </c>
       <c r="BI27" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ27" s="11">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BK27" s="80">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BL27" s="16">
+        <f t="shared" si="13"/>
+        <v>0.375</v>
+      </c>
+      <c r="BM27" s="31">
+        <f t="shared" si="14"/>
+        <v>0.7395833333321207</v>
+      </c>
+      <c r="BN27" s="81">
+        <f t="shared" ref="BN27:BQ27" si="64">TEXT(MAX(0,MIN($BM27,BN$7)-MAX($BL27,BN$6)),"h:mm")*24</f>
+        <v>3</v>
+      </c>
+      <c r="BO27" s="82">
+        <f t="shared" si="64"/>
+        <v>1</v>
+      </c>
+      <c r="BP27" s="82">
+        <f t="shared" si="64"/>
+        <v>4.75</v>
+      </c>
+      <c r="BQ27" s="82">
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="BR27" s="82">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BK27" s="80">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BL27" s="16">
+      <c r="BS27" s="82">
+        <f t="shared" ref="BS27:BT27" si="65">TEXT(MAX(0,MIN($BM27,BS$7)-MAX($BL27,BS$6)),"h:mm")*24</f>
+        <v>0</v>
+      </c>
+      <c r="BT27" s="83">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="BU27" s="82">
         <f t="shared" si="18"/>
-        <v>0.375</v>
-      </c>
-      <c r="BM27" s="31">
+        <v>7.75</v>
+      </c>
+      <c r="BV27" s="82">
         <f t="shared" si="19"/>
-        <v>0.7395833333321207</v>
-      </c>
-      <c r="BN27" s="81">
-        <f t="shared" ref="BN27:BQ27" si="83">TEXT(MAX(0,MIN($BM27,BN$7)-MAX($BL27,BN$6)),"h:mm")*24</f>
-        <v>3</v>
-      </c>
-      <c r="BO27" s="82">
-        <f t="shared" si="83"/>
-        <v>1</v>
-      </c>
-      <c r="BP27" s="82">
-        <f t="shared" si="83"/>
-        <v>4.75</v>
-      </c>
-      <c r="BQ27" s="82">
-        <f t="shared" si="83"/>
-        <v>0</v>
-      </c>
-      <c r="BR27" s="82">
+        <v>0</v>
+      </c>
+      <c r="BW27" s="82">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="BX27" s="82">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="BS27" s="82">
-        <f t="shared" ref="BS27:BT27" si="84">TEXT(MAX(0,MIN($BM27,BS$7)-MAX($BL27,BS$6)),"h:mm")*24</f>
-        <v>0</v>
-      </c>
-      <c r="BT27" s="83">
-        <f t="shared" si="84"/>
-        <v>0</v>
-      </c>
-      <c r="BU27" s="82">
+      <c r="BY27" s="82">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BZ27" s="84">
         <f t="shared" si="23"/>
-        <v>7.75</v>
-      </c>
-      <c r="BV27" s="82">
+        <v>0</v>
+      </c>
+      <c r="CA27" s="84">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="BW27" s="82">
+      <c r="CB27" s="84">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="BX27" s="82">
+      <c r="CC27" s="82">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="BY27" s="82">
+      <c r="CD27" s="11">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BZ27" s="84">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="CA27" s="84">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="CB27" s="84">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CC27" s="82">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="CD27" s="11">
-        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="CE27" s="11"/>
@@ -6554,30 +6589,28 @@
       <c r="L28" s="55"/>
       <c r="M28" s="67">
         <f>IF(E28="","",IF((BO28+BQ28)=0,"",(BO28+BQ28)*60))</f>
-        <v>60</v>
       </c>
       <c r="N28" s="55"/>
       <c r="O28" s="68">
-        <f t="shared" si="82"/>
-        <v>0.3229166666678793</v>
+        <f>IF(E28&lt;&gt;"",IF(BU28&lt;&gt;0,BU28/24,""),"")</f>
       </c>
       <c r="P28" s="26"/>
       <c r="Q28" s="26"/>
       <c r="R28" s="55"/>
       <c r="S28" s="68">
-        <f t="shared" si="61"/>
+        <f>IF(E28&lt;&gt;"",IF(BY28&lt;&gt;0,BY28/24,""),"")</f>
       </c>
       <c r="T28" s="26"/>
       <c r="U28" s="26"/>
       <c r="V28" s="55"/>
       <c r="W28" s="68">
-        <f t="shared" si="8"/>
+        <f>IF(E28&lt;&gt;"",IF(BS28&lt;&gt;0,BS28/24,""),"")</f>
       </c>
       <c r="X28" s="26"/>
       <c r="Y28" s="26"/>
       <c r="Z28" s="55"/>
       <c r="AA28" s="68">
-        <f t="shared" si="79"/>
+        <f>IF(E28&lt;&gt;"",IF(CA28&lt;&gt;0,CA28/24,""),"")</f>
       </c>
       <c r="AB28" s="26"/>
       <c r="AC28" s="26"/>
@@ -6594,7 +6627,7 @@
       <c r="AN28" s="72"/>
       <c r="AO28" s="55"/>
       <c r="AP28" s="73">
-        <f t="shared" si="10"/>
+        <f>IF(OR(AJ28&lt;&gt;"",AN28&lt;&gt;"",(BV28+BW28)&lt;&gt;0),IF(CD28=1,"","要"),IF(OR(S28&lt;&gt;"",W28&lt;&gt;"",AA28&lt;&gt;""),"申",""))</f>
       </c>
       <c r="AQ28" s="94" t="s">
         <v>88</v>
@@ -6612,19 +6645,19 @@
       <c r="BB28" s="37"/>
       <c r="BC28" s="3"/>
       <c r="BD28" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BE28" s="11">
-        <f t="shared" si="62"/>
+        <f t="shared" si="48"/>
         <v>2026</v>
       </c>
       <c r="BF28" s="11">
-        <f t="shared" si="63"/>
+        <f t="shared" si="49"/>
         <v>9</v>
       </c>
       <c r="BG28" s="11" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>2026/9/9</v>
       </c>
       <c r="BH28" s="79">
@@ -6632,91 +6665,91 @@
         <v>1</v>
       </c>
       <c r="BI28" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ28" s="11">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BK28" s="80">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BL28" s="16">
+        <f t="shared" si="13"/>
+        <v>0.375</v>
+      </c>
+      <c r="BM28" s="31">
+        <f t="shared" si="14"/>
+        <v>0.7395833333321207</v>
+      </c>
+      <c r="BN28" s="81">
+        <f t="shared" ref="BN28:BQ28" si="66">TEXT(MAX(0,MIN($BM28,BN$7)-MAX($BL28,BN$6)),"h:mm")*24</f>
+        <v>3</v>
+      </c>
+      <c r="BO28" s="82">
+        <f t="shared" si="66"/>
+        <v>1</v>
+      </c>
+      <c r="BP28" s="82">
+        <f t="shared" si="66"/>
+        <v>4.75</v>
+      </c>
+      <c r="BQ28" s="82">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
+      <c r="BR28" s="82">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BK28" s="80">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BL28" s="16">
+      <c r="BS28" s="82">
+        <f t="shared" ref="BS28:BT28" si="67">TEXT(MAX(0,MIN($BM28,BS$7)-MAX($BL28,BS$6)),"h:mm")*24</f>
+        <v>0</v>
+      </c>
+      <c r="BT28" s="83">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="BU28" s="82">
         <f t="shared" si="18"/>
-        <v>0.375</v>
-      </c>
-      <c r="BM28" s="31">
+        <v>7.75</v>
+      </c>
+      <c r="BV28" s="82">
         <f t="shared" si="19"/>
-        <v>0.7395833333321207</v>
-      </c>
-      <c r="BN28" s="81">
-        <f t="shared" ref="BN28:BQ28" si="85">TEXT(MAX(0,MIN($BM28,BN$7)-MAX($BL28,BN$6)),"h:mm")*24</f>
-        <v>3</v>
-      </c>
-      <c r="BO28" s="82">
-        <f t="shared" si="85"/>
-        <v>1</v>
-      </c>
-      <c r="BP28" s="82">
-        <f t="shared" si="85"/>
-        <v>4.75</v>
-      </c>
-      <c r="BQ28" s="82">
-        <f t="shared" si="85"/>
-        <v>0</v>
-      </c>
-      <c r="BR28" s="82">
+        <v>0</v>
+      </c>
+      <c r="BW28" s="82">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="BX28" s="82">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="BS28" s="82">
-        <f t="shared" ref="BS28:BT28" si="86">TEXT(MAX(0,MIN($BM28,BS$7)-MAX($BL28,BS$6)),"h:mm")*24</f>
-        <v>0</v>
-      </c>
-      <c r="BT28" s="83">
-        <f t="shared" si="86"/>
-        <v>0</v>
-      </c>
-      <c r="BU28" s="82">
+      <c r="BY28" s="82">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BZ28" s="84">
         <f t="shared" si="23"/>
-        <v>7.75</v>
-      </c>
-      <c r="BV28" s="82">
+        <v>0</v>
+      </c>
+      <c r="CA28" s="84">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="BW28" s="82">
+      <c r="CB28" s="84">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="BX28" s="82">
+      <c r="CC28" s="82">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="BY28" s="82">
+      <c r="CD28" s="11">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BZ28" s="84">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="CA28" s="84">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="CB28" s="84">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CC28" s="82">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="CD28" s="11">
-        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="CE28" s="11"/>
@@ -6746,31 +6779,29 @@
       <c r="K29" s="66"/>
       <c r="L29" s="55"/>
       <c r="M29" s="67">
-        <f t="shared" ref="M29" si="87">IF(E29="","",IF((BO29+BQ29)=0,"",(BO29+BQ29)*60))</f>
-        <v>60</v>
+        <f>IF(E29="","",IF((BO29+BQ29)=0,"",(BO29+BQ29)*60))</f>
       </c>
       <c r="N29" s="55"/>
       <c r="O29" s="68">
-        <f t="shared" ref="O29:O30" si="88">IF(E29&lt;&gt;"",IF(BU29&lt;&gt;0,BU29/24,""),"")</f>
-        <v>0.3229166666678793</v>
+        <f>IF(E29&lt;&gt;"",IF(BU29&lt;&gt;0,BU29/24,""),"")</f>
       </c>
       <c r="P29" s="26"/>
       <c r="Q29" s="26"/>
       <c r="R29" s="55"/>
       <c r="S29" s="68">
-        <f t="shared" si="61"/>
+        <f>IF(E29&lt;&gt;"",IF(BY29&lt;&gt;0,BY29/24,""),"")</f>
       </c>
       <c r="T29" s="26"/>
       <c r="U29" s="26"/>
       <c r="V29" s="55"/>
       <c r="W29" s="68">
-        <f t="shared" si="8"/>
+        <f>IF(E29&lt;&gt;"",IF(BS29&lt;&gt;0,BS29/24,""),"")</f>
       </c>
       <c r="X29" s="26"/>
       <c r="Y29" s="26"/>
       <c r="Z29" s="55"/>
       <c r="AA29" s="68">
-        <f t="shared" si="79"/>
+        <f>IF(E29&lt;&gt;"",IF(CA29&lt;&gt;0,CA29/24,""),"")</f>
       </c>
       <c r="AB29" s="26"/>
       <c r="AC29" s="26"/>
@@ -6787,7 +6818,7 @@
       <c r="AN29" s="72"/>
       <c r="AO29" s="55"/>
       <c r="AP29" s="73">
-        <f t="shared" si="10"/>
+        <f>IF(OR(AJ29&lt;&gt;"",AN29&lt;&gt;"",(BV29+BW29)&lt;&gt;0),IF(CD29=1,"","要"),IF(OR(S29&lt;&gt;"",W29&lt;&gt;"",AA29&lt;&gt;""),"申",""))</f>
       </c>
       <c r="AQ29" s="47"/>
       <c r="AR29" s="14"/>
@@ -6803,19 +6834,19 @@
       <c r="BB29" s="48"/>
       <c r="BC29" s="3"/>
       <c r="BD29" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BE29" s="11">
-        <f t="shared" si="62"/>
+        <f t="shared" si="48"/>
         <v>2026</v>
       </c>
       <c r="BF29" s="11">
-        <f t="shared" si="63"/>
+        <f t="shared" si="49"/>
         <v>9</v>
       </c>
       <c r="BG29" s="11" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>2026/9/10</v>
       </c>
       <c r="BH29" s="79">
@@ -6823,91 +6854,91 @@
         <v>1</v>
       </c>
       <c r="BI29" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ29" s="11">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BK29" s="80">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BL29" s="16">
+        <f t="shared" si="13"/>
+        <v>0.375</v>
+      </c>
+      <c r="BM29" s="31">
+        <f t="shared" si="14"/>
+        <v>0.7395833333321207</v>
+      </c>
+      <c r="BN29" s="81">
+        <f t="shared" ref="BN29:BQ29" si="68">TEXT(MAX(0,MIN($BM29,BN$7)-MAX($BL29,BN$6)),"h:mm")*24</f>
+        <v>3</v>
+      </c>
+      <c r="BO29" s="82">
+        <f t="shared" si="68"/>
+        <v>1</v>
+      </c>
+      <c r="BP29" s="82">
+        <f t="shared" si="68"/>
+        <v>4.75</v>
+      </c>
+      <c r="BQ29" s="82">
+        <f t="shared" si="68"/>
+        <v>0</v>
+      </c>
+      <c r="BR29" s="82">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BK29" s="80">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BL29" s="16">
+      <c r="BS29" s="82">
+        <f t="shared" ref="BS29:BT29" si="69">TEXT(MAX(0,MIN($BM29,BS$7)-MAX($BL29,BS$6)),"h:mm")*24</f>
+        <v>0</v>
+      </c>
+      <c r="BT29" s="83">
+        <f t="shared" si="69"/>
+        <v>0</v>
+      </c>
+      <c r="BU29" s="82">
         <f t="shared" si="18"/>
-        <v>0.375</v>
-      </c>
-      <c r="BM29" s="31">
+        <v>7.75</v>
+      </c>
+      <c r="BV29" s="82">
         <f t="shared" si="19"/>
-        <v>0.7395833333321207</v>
-      </c>
-      <c r="BN29" s="81">
-        <f t="shared" ref="BN29:BQ29" si="89">TEXT(MAX(0,MIN($BM29,BN$7)-MAX($BL29,BN$6)),"h:mm")*24</f>
-        <v>3</v>
-      </c>
-      <c r="BO29" s="82">
-        <f t="shared" si="89"/>
-        <v>1</v>
-      </c>
-      <c r="BP29" s="82">
-        <f t="shared" si="89"/>
-        <v>4.75</v>
-      </c>
-      <c r="BQ29" s="82">
-        <f t="shared" si="89"/>
-        <v>0</v>
-      </c>
-      <c r="BR29" s="82">
+        <v>0</v>
+      </c>
+      <c r="BW29" s="82">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="BX29" s="82">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="BS29" s="82">
-        <f t="shared" ref="BS29:BT29" si="90">TEXT(MAX(0,MIN($BM29,BS$7)-MAX($BL29,BS$6)),"h:mm")*24</f>
-        <v>0</v>
-      </c>
-      <c r="BT29" s="83">
-        <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
-      <c r="BU29" s="82">
+      <c r="BY29" s="82">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BZ29" s="84">
         <f t="shared" si="23"/>
-        <v>7.75</v>
-      </c>
-      <c r="BV29" s="82">
+        <v>0</v>
+      </c>
+      <c r="CA29" s="84">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="BW29" s="82">
+      <c r="CB29" s="84">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="BX29" s="82">
+      <c r="CC29" s="82">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="BY29" s="82">
+      <c r="CD29" s="11">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BZ29" s="84">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="CA29" s="84">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="CB29" s="84">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CC29" s="82">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="CD29" s="11">
-        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="CE29" s="11"/>
@@ -6938,25 +6969,29 @@
       <c r="L30" s="55"/>
       <c r="M30" s="67">
         <f>IF(E30="","",IF((BO30+BQ30)=0,"",(BO30+BQ30)*60))</f>
-        <v>60</v>
       </c>
       <c r="N30" s="55"/>
       <c r="O30" s="68">
-        <f t="shared" si="88"/>
-        <v>0.3229166666678793</v>
+        <f>IF(E30&lt;&gt;"",IF(BU30&lt;&gt;0,BU30/24,""),"")</f>
       </c>
       <c r="P30" s="26"/>
       <c r="Q30" s="26"/>
       <c r="R30" s="55"/>
-      <c r="S30" s="68"/>
+      <c r="S30" s="68">
+        <f>IF(E30&lt;&gt;"",IF(BY30&lt;&gt;0,BY30/24,""),"")</f>
+      </c>
       <c r="T30" s="26"/>
       <c r="U30" s="26"/>
       <c r="V30" s="55"/>
-      <c r="W30" s="68"/>
+      <c r="W30" s="68">
+        <f>IF(E30&lt;&gt;"",IF(BS30&lt;&gt;0,BS30/24,""),"")</f>
+      </c>
       <c r="X30" s="26"/>
       <c r="Y30" s="26"/>
       <c r="Z30" s="55"/>
-      <c r="AA30" s="68"/>
+      <c r="AA30" s="68">
+        <f>IF(E30&lt;&gt;"",IF(CA30&lt;&gt;0,CA30/24,""),"")</f>
+      </c>
       <c r="AB30" s="26"/>
       <c r="AC30" s="26"/>
       <c r="AD30" s="55"/>
@@ -6972,7 +7007,7 @@
       <c r="AN30" s="72"/>
       <c r="AO30" s="55"/>
       <c r="AP30" s="73">
-        <f t="shared" si="10"/>
+        <f>IF(OR(AJ30&lt;&gt;"",AN30&lt;&gt;"",(BV30+BW30)&lt;&gt;0),IF(CD30=1,"","要"),IF(OR(S30&lt;&gt;"",W30&lt;&gt;"",AA30&lt;&gt;""),"申",""))</f>
       </c>
       <c r="AQ30" s="54" t="s">
         <v>89</v>
@@ -6990,19 +7025,19 @@
       <c r="BB30" s="55"/>
       <c r="BC30" s="3"/>
       <c r="BD30" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BE30" s="11">
-        <f t="shared" si="62"/>
+        <f t="shared" si="48"/>
         <v>2026</v>
       </c>
       <c r="BF30" s="11">
-        <f t="shared" si="63"/>
+        <f t="shared" si="49"/>
         <v>9</v>
       </c>
       <c r="BG30" s="11" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>2026/9/11</v>
       </c>
       <c r="BH30" s="79">
@@ -7010,91 +7045,91 @@
         <v>1</v>
       </c>
       <c r="BI30" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ30" s="11">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BK30" s="80">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BL30" s="16">
+        <f t="shared" si="13"/>
+        <v>0.375</v>
+      </c>
+      <c r="BM30" s="31">
+        <f t="shared" si="14"/>
+        <v>0.7395833333321207</v>
+      </c>
+      <c r="BN30" s="81">
+        <f t="shared" ref="BN30:BQ30" si="70">TEXT(MAX(0,MIN($BM30,BN$7)-MAX($BL30,BN$6)),"h:mm")*24</f>
+        <v>3</v>
+      </c>
+      <c r="BO30" s="82">
+        <f t="shared" si="70"/>
+        <v>1</v>
+      </c>
+      <c r="BP30" s="82">
+        <f t="shared" si="70"/>
+        <v>4.75</v>
+      </c>
+      <c r="BQ30" s="82">
+        <f t="shared" si="70"/>
+        <v>0</v>
+      </c>
+      <c r="BR30" s="82">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BK30" s="80">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BL30" s="16">
+      <c r="BS30" s="82">
+        <f t="shared" ref="BS30:BT30" si="71">TEXT(MAX(0,MIN($BM30,BS$7)-MAX($BL30,BS$6)),"h:mm")*24</f>
+        <v>0</v>
+      </c>
+      <c r="BT30" s="83">
+        <f t="shared" si="71"/>
+        <v>0</v>
+      </c>
+      <c r="BU30" s="82">
         <f t="shared" si="18"/>
-        <v>0.375</v>
-      </c>
-      <c r="BM30" s="31">
+        <v>7.75</v>
+      </c>
+      <c r="BV30" s="82">
         <f t="shared" si="19"/>
-        <v>0.7395833333321207</v>
-      </c>
-      <c r="BN30" s="81">
-        <f t="shared" ref="BN30:BQ30" si="91">TEXT(MAX(0,MIN($BM30,BN$7)-MAX($BL30,BN$6)),"h:mm")*24</f>
-        <v>3</v>
-      </c>
-      <c r="BO30" s="82">
-        <f t="shared" si="91"/>
-        <v>1</v>
-      </c>
-      <c r="BP30" s="82">
-        <f t="shared" si="91"/>
-        <v>4.75</v>
-      </c>
-      <c r="BQ30" s="82">
-        <f t="shared" si="91"/>
-        <v>0</v>
-      </c>
-      <c r="BR30" s="82">
+        <v>0</v>
+      </c>
+      <c r="BW30" s="82">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="BX30" s="82">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="BS30" s="82">
-        <f t="shared" ref="BS30:BT30" si="92">TEXT(MAX(0,MIN($BM30,BS$7)-MAX($BL30,BS$6)),"h:mm")*24</f>
-        <v>0</v>
-      </c>
-      <c r="BT30" s="83">
-        <f t="shared" si="92"/>
-        <v>0</v>
-      </c>
-      <c r="BU30" s="82">
+      <c r="BY30" s="82">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BZ30" s="84">
         <f t="shared" si="23"/>
-        <v>7.75</v>
-      </c>
-      <c r="BV30" s="82">
+        <v>0</v>
+      </c>
+      <c r="CA30" s="84">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="BW30" s="82">
+      <c r="CB30" s="84">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="BX30" s="82">
+      <c r="CC30" s="82">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="BY30" s="82">
+      <c r="CD30" s="11">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BZ30" s="84">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="CA30" s="84">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="CB30" s="84">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CC30" s="82">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="CD30" s="11">
-        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="CE30" s="11"/>
@@ -7123,21 +7158,31 @@
       <c r="J31" s="65"/>
       <c r="K31" s="66"/>
       <c r="L31" s="55"/>
-      <c r="M31" s="67"/>
+      <c r="M31" s="67">
+        <f>IF(E31="","",IF((BO31+BQ31)=0,"",(BO31+BQ31)*60))</f>
+      </c>
       <c r="N31" s="55"/>
-      <c r="O31" s="68"/>
+      <c r="O31" s="68">
+        <f>IF(E31&lt;&gt;"",IF(BU31&lt;&gt;0,BU31/24,""),"")</f>
+      </c>
       <c r="P31" s="26"/>
       <c r="Q31" s="26"/>
       <c r="R31" s="55"/>
-      <c r="S31" s="68"/>
+      <c r="S31" s="68">
+        <f>IF(E31&lt;&gt;"",IF(BY31&lt;&gt;0,BY31/24,""),"")</f>
+      </c>
       <c r="T31" s="26"/>
       <c r="U31" s="26"/>
       <c r="V31" s="55"/>
-      <c r="W31" s="68"/>
+      <c r="W31" s="68">
+        <f>IF(E31&lt;&gt;"",IF(BS31&lt;&gt;0,BS31/24,""),"")</f>
+      </c>
       <c r="X31" s="26"/>
       <c r="Y31" s="26"/>
       <c r="Z31" s="55"/>
-      <c r="AA31" s="68"/>
+      <c r="AA31" s="68">
+        <f>IF(E31&lt;&gt;"",IF(CA31&lt;&gt;0,CA31/24,""),"")</f>
+      </c>
       <c r="AB31" s="26"/>
       <c r="AC31" s="26"/>
       <c r="AD31" s="55"/>
@@ -7153,7 +7198,7 @@
       <c r="AN31" s="72"/>
       <c r="AO31" s="55"/>
       <c r="AP31" s="73">
-        <f t="shared" si="10"/>
+        <f>IF(OR(AJ31&lt;&gt;"",AN31&lt;&gt;"",(BV31+BW31)&lt;&gt;0),IF(CD31=1,"","要"),IF(OR(S31&lt;&gt;"",W31&lt;&gt;"",AA31&lt;&gt;""),"申",""))</f>
       </c>
       <c r="AQ31" s="96"/>
       <c r="AR31" s="29"/>
@@ -7169,19 +7214,19 @@
       <c r="BB31" s="37"/>
       <c r="BC31" s="3"/>
       <c r="BD31" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BE31" s="11">
-        <f t="shared" si="62"/>
+        <f t="shared" si="48"/>
         <v>2026</v>
       </c>
       <c r="BF31" s="11">
-        <f t="shared" si="63"/>
+        <f t="shared" si="49"/>
         <v>9</v>
       </c>
       <c r="BG31" s="11" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>2026/9/12</v>
       </c>
       <c r="BH31" s="79">
@@ -7189,91 +7234,91 @@
         <v>0</v>
       </c>
       <c r="BI31" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ31" s="11">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BK31" s="80">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BL31" s="16">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="BM31" s="31">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="BN31" s="81">
+        <f t="shared" ref="BN31:BQ31" si="72">TEXT(MAX(0,MIN($BM31,BN$7)-MAX($BL31,BN$6)),"h:mm")*24</f>
+        <v>0</v>
+      </c>
+      <c r="BO31" s="82">
+        <f t="shared" si="72"/>
+        <v>0</v>
+      </c>
+      <c r="BP31" s="82">
+        <f t="shared" si="72"/>
+        <v>0</v>
+      </c>
+      <c r="BQ31" s="82">
+        <f t="shared" si="72"/>
+        <v>0</v>
+      </c>
+      <c r="BR31" s="82">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BK31" s="80">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BL31" s="16">
+      <c r="BS31" s="82">
+        <f t="shared" ref="BS31:BT31" si="73">TEXT(MAX(0,MIN($BM31,BS$7)-MAX($BL31,BS$6)),"h:mm")*24</f>
+        <v>0</v>
+      </c>
+      <c r="BT31" s="83">
+        <f t="shared" si="73"/>
+        <v>0</v>
+      </c>
+      <c r="BU31" s="82">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BM31" s="31">
+      <c r="BV31" s="82">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="BN31" s="81">
-        <f t="shared" ref="BN31:BQ31" si="93">TEXT(MAX(0,MIN($BM31,BN$7)-MAX($BL31,BN$6)),"h:mm")*24</f>
-        <v>0</v>
-      </c>
-      <c r="BO31" s="82">
-        <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="BP31" s="82">
-        <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="BQ31" s="82">
-        <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="BR31" s="82">
+      <c r="BW31" s="82">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="BX31" s="82">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="BS31" s="82">
-        <f t="shared" ref="BS31:BT31" si="94">TEXT(MAX(0,MIN($BM31,BS$7)-MAX($BL31,BS$6)),"h:mm")*24</f>
-        <v>0</v>
-      </c>
-      <c r="BT31" s="83">
-        <f t="shared" si="94"/>
-        <v>0</v>
-      </c>
-      <c r="BU31" s="82">
+      <c r="BY31" s="82">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BZ31" s="84">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="BV31" s="82">
+      <c r="CA31" s="84">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="BW31" s="82">
+      <c r="CB31" s="84">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="BX31" s="82">
+      <c r="CC31" s="82">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="BY31" s="82">
+      <c r="CD31" s="11">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BZ31" s="84">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="CA31" s="84">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="CB31" s="84">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CC31" s="82">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="CD31" s="11">
-        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="CE31" s="11"/>
@@ -7302,21 +7347,31 @@
       <c r="J32" s="65"/>
       <c r="K32" s="66"/>
       <c r="L32" s="55"/>
-      <c r="M32" s="67"/>
+      <c r="M32" s="67">
+        <f>IF(E32="","",IF((BO32+BQ32)=0,"",(BO32+BQ32)*60))</f>
+      </c>
       <c r="N32" s="55"/>
-      <c r="O32" s="68"/>
+      <c r="O32" s="68">
+        <f>IF(E32&lt;&gt;"",IF(BU32&lt;&gt;0,BU32/24,""),"")</f>
+      </c>
       <c r="P32" s="26"/>
       <c r="Q32" s="26"/>
       <c r="R32" s="55"/>
-      <c r="S32" s="68"/>
+      <c r="S32" s="68">
+        <f>IF(E32&lt;&gt;"",IF(BY32&lt;&gt;0,BY32/24,""),"")</f>
+      </c>
       <c r="T32" s="26"/>
       <c r="U32" s="26"/>
       <c r="V32" s="55"/>
-      <c r="W32" s="68"/>
+      <c r="W32" s="68">
+        <f>IF(E32&lt;&gt;"",IF(BS32&lt;&gt;0,BS32/24,""),"")</f>
+      </c>
       <c r="X32" s="26"/>
       <c r="Y32" s="26"/>
       <c r="Z32" s="55"/>
-      <c r="AA32" s="68"/>
+      <c r="AA32" s="68">
+        <f>IF(E32&lt;&gt;"",IF(CA32&lt;&gt;0,CA32/24,""),"")</f>
+      </c>
       <c r="AB32" s="26"/>
       <c r="AC32" s="26"/>
       <c r="AD32" s="55"/>
@@ -7332,7 +7387,7 @@
       <c r="AN32" s="72"/>
       <c r="AO32" s="55"/>
       <c r="AP32" s="73">
-        <f t="shared" si="10"/>
+        <f>IF(OR(AJ32&lt;&gt;"",AN32&lt;&gt;"",(BV32+BW32)&lt;&gt;0),IF(CD32=1,"","要"),IF(OR(S32&lt;&gt;"",W32&lt;&gt;"",AA32&lt;&gt;""),"申",""))</f>
       </c>
       <c r="AQ32" s="49"/>
       <c r="AR32" s="2"/>
@@ -7348,19 +7403,19 @@
       <c r="BB32" s="44"/>
       <c r="BC32" s="3"/>
       <c r="BD32" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BE32" s="11">
-        <f t="shared" si="62"/>
+        <f t="shared" si="48"/>
         <v>2026</v>
       </c>
       <c r="BF32" s="11">
-        <f t="shared" si="63"/>
+        <f t="shared" si="49"/>
         <v>9</v>
       </c>
       <c r="BG32" s="11" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>2026/9/13</v>
       </c>
       <c r="BH32" s="79">
@@ -7368,91 +7423,91 @@
         <v>0</v>
       </c>
       <c r="BI32" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ32" s="11">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BK32" s="80">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BL32" s="16">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="BM32" s="31">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="BN32" s="81">
+        <f t="shared" ref="BN32:BQ32" si="74">TEXT(MAX(0,MIN($BM32,BN$7)-MAX($BL32,BN$6)),"h:mm")*24</f>
+        <v>0</v>
+      </c>
+      <c r="BO32" s="82">
+        <f t="shared" si="74"/>
+        <v>0</v>
+      </c>
+      <c r="BP32" s="82">
+        <f t="shared" si="74"/>
+        <v>0</v>
+      </c>
+      <c r="BQ32" s="82">
+        <f t="shared" si="74"/>
+        <v>0</v>
+      </c>
+      <c r="BR32" s="82">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BK32" s="80">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BL32" s="16">
+      <c r="BS32" s="82">
+        <f t="shared" ref="BS32:BT32" si="75">TEXT(MAX(0,MIN($BM32,BS$7)-MAX($BL32,BS$6)),"h:mm")*24</f>
+        <v>0</v>
+      </c>
+      <c r="BT32" s="83">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="BU32" s="82">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BM32" s="31">
+      <c r="BV32" s="82">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="BN32" s="81">
-        <f t="shared" ref="BN32:BQ32" si="95">TEXT(MAX(0,MIN($BM32,BN$7)-MAX($BL32,BN$6)),"h:mm")*24</f>
-        <v>0</v>
-      </c>
-      <c r="BO32" s="82">
-        <f t="shared" si="95"/>
-        <v>0</v>
-      </c>
-      <c r="BP32" s="82">
-        <f t="shared" si="95"/>
-        <v>0</v>
-      </c>
-      <c r="BQ32" s="82">
-        <f t="shared" si="95"/>
-        <v>0</v>
-      </c>
-      <c r="BR32" s="82">
+      <c r="BW32" s="82">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="BX32" s="82">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="BS32" s="82">
-        <f t="shared" ref="BS32:BT32" si="96">TEXT(MAX(0,MIN($BM32,BS$7)-MAX($BL32,BS$6)),"h:mm")*24</f>
-        <v>0</v>
-      </c>
-      <c r="BT32" s="83">
-        <f t="shared" si="96"/>
-        <v>0</v>
-      </c>
-      <c r="BU32" s="82">
+      <c r="BY32" s="82">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BZ32" s="84">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="BV32" s="82">
+      <c r="CA32" s="84">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="BW32" s="82">
+      <c r="CB32" s="84">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="BX32" s="82">
+      <c r="CC32" s="82">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="BY32" s="82">
+      <c r="CD32" s="11">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BZ32" s="84">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="CA32" s="84">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="CB32" s="84">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CC32" s="82">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="CD32" s="11">
-        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="CE32" s="11"/>
@@ -7479,21 +7534,31 @@
       <c r="J33" s="65"/>
       <c r="K33" s="66"/>
       <c r="L33" s="55"/>
-      <c r="M33" s="67"/>
+      <c r="M33" s="67">
+        <f>IF(E33="","",IF((BO33+BQ33)=0,"",(BO33+BQ33)*60))</f>
+      </c>
       <c r="N33" s="55"/>
-      <c r="O33" s="68"/>
+      <c r="O33" s="68">
+        <f>IF(E33&lt;&gt;"",IF(BU33&lt;&gt;0,BU33/24,""),"")</f>
+      </c>
       <c r="P33" s="26"/>
       <c r="Q33" s="26"/>
       <c r="R33" s="55"/>
-      <c r="S33" s="68"/>
+      <c r="S33" s="68">
+        <f>IF(E33&lt;&gt;"",IF(BY33&lt;&gt;0,BY33/24,""),"")</f>
+      </c>
       <c r="T33" s="26"/>
       <c r="U33" s="26"/>
       <c r="V33" s="55"/>
-      <c r="W33" s="68"/>
+      <c r="W33" s="68">
+        <f>IF(E33&lt;&gt;"",IF(BS33&lt;&gt;0,BS33/24,""),"")</f>
+      </c>
       <c r="X33" s="26"/>
       <c r="Y33" s="26"/>
       <c r="Z33" s="55"/>
-      <c r="AA33" s="68"/>
+      <c r="AA33" s="68">
+        <f>IF(E33&lt;&gt;"",IF(CA33&lt;&gt;0,CA33/24,""),"")</f>
+      </c>
       <c r="AB33" s="26"/>
       <c r="AC33" s="26"/>
       <c r="AD33" s="55"/>
@@ -7509,7 +7574,7 @@
       <c r="AN33" s="72"/>
       <c r="AO33" s="55"/>
       <c r="AP33" s="73">
-        <f t="shared" si="10"/>
+        <f>IF(OR(AJ33&lt;&gt;"",AN33&lt;&gt;"",(BV33+BW33)&lt;&gt;0),IF(CD33=1,"","要"),IF(OR(S33&lt;&gt;"",W33&lt;&gt;"",AA33&lt;&gt;""),"申",""))</f>
       </c>
       <c r="AQ33" s="49"/>
       <c r="AR33" s="2"/>
@@ -7525,19 +7590,19 @@
       <c r="BB33" s="44"/>
       <c r="BC33" s="3"/>
       <c r="BD33" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BE33" s="11">
-        <f t="shared" si="62"/>
+        <f t="shared" si="48"/>
         <v>2026</v>
       </c>
       <c r="BF33" s="11">
-        <f t="shared" si="63"/>
+        <f t="shared" si="49"/>
         <v>9</v>
       </c>
       <c r="BG33" s="11" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>2026/9/14</v>
       </c>
       <c r="BH33" s="79">
@@ -7545,91 +7610,91 @@
         <v>0</v>
       </c>
       <c r="BI33" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ33" s="11">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BK33" s="80">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BL33" s="16">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="BM33" s="31">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="BN33" s="81">
+        <f t="shared" ref="BN33:BQ33" si="76">TEXT(MAX(0,MIN($BM33,BN$7)-MAX($BL33,BN$6)),"h:mm")*24</f>
+        <v>0</v>
+      </c>
+      <c r="BO33" s="82">
+        <f t="shared" si="76"/>
+        <v>0</v>
+      </c>
+      <c r="BP33" s="82">
+        <f t="shared" si="76"/>
+        <v>0</v>
+      </c>
+      <c r="BQ33" s="82">
+        <f t="shared" si="76"/>
+        <v>0</v>
+      </c>
+      <c r="BR33" s="82">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BK33" s="80">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BL33" s="16">
+      <c r="BS33" s="82">
+        <f t="shared" ref="BS33:BT33" si="77">TEXT(MAX(0,MIN($BM33,BS$7)-MAX($BL33,BS$6)),"h:mm")*24</f>
+        <v>0</v>
+      </c>
+      <c r="BT33" s="83">
+        <f t="shared" si="77"/>
+        <v>0</v>
+      </c>
+      <c r="BU33" s="82">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BM33" s="31">
+      <c r="BV33" s="82">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="BN33" s="81">
-        <f t="shared" ref="BN33:BQ33" si="97">TEXT(MAX(0,MIN($BM33,BN$7)-MAX($BL33,BN$6)),"h:mm")*24</f>
-        <v>0</v>
-      </c>
-      <c r="BO33" s="82">
-        <f t="shared" si="97"/>
-        <v>0</v>
-      </c>
-      <c r="BP33" s="82">
-        <f t="shared" si="97"/>
-        <v>0</v>
-      </c>
-      <c r="BQ33" s="82">
-        <f t="shared" si="97"/>
-        <v>0</v>
-      </c>
-      <c r="BR33" s="82">
+      <c r="BW33" s="82">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="BX33" s="82">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="BS33" s="82">
-        <f t="shared" ref="BS33:BT33" si="98">TEXT(MAX(0,MIN($BM33,BS$7)-MAX($BL33,BS$6)),"h:mm")*24</f>
-        <v>0</v>
-      </c>
-      <c r="BT33" s="83">
-        <f t="shared" si="98"/>
-        <v>0</v>
-      </c>
-      <c r="BU33" s="82">
+      <c r="BY33" s="82">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BZ33" s="84">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="BV33" s="82">
+      <c r="CA33" s="84">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="BW33" s="82">
+      <c r="CB33" s="84">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="BX33" s="82">
+      <c r="CC33" s="82">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="BY33" s="82">
+      <c r="CD33" s="11">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BZ33" s="84">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="CA33" s="84">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="CB33" s="84">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CC33" s="82">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="CD33" s="11">
-        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="CE33" s="11"/>
@@ -7657,29 +7722,29 @@
       <c r="K34" s="66"/>
       <c r="L34" s="55"/>
       <c r="M34" s="67">
-        <f t="shared" ref="M34" si="99">IF(E34="","",IF((BO34+BQ34)=0,"",(BO34+BQ34)*60))</f>
+        <f>IF(E34="","",IF((BO34+BQ34)=0,"",(BO34+BQ34)*60))</f>
       </c>
       <c r="N34" s="55"/>
       <c r="O34" s="68">
-        <f t="shared" ref="O34:O35" si="100">IF(E34&lt;&gt;"",IF(BU34&lt;&gt;0,BU34/24,""),"")</f>
+        <f>IF(E34&lt;&gt;"",IF(BU34&lt;&gt;0,BU34/24,""),"")</f>
       </c>
       <c r="P34" s="26"/>
       <c r="Q34" s="26"/>
       <c r="R34" s="55"/>
       <c r="S34" s="68">
-        <f t="shared" si="61"/>
+        <f>IF(E34&lt;&gt;"",IF(BY34&lt;&gt;0,BY34/24,""),"")</f>
       </c>
       <c r="T34" s="26"/>
       <c r="U34" s="26"/>
       <c r="V34" s="55"/>
       <c r="W34" s="68">
-        <f t="shared" si="8"/>
+        <f>IF(E34&lt;&gt;"",IF(BS34&lt;&gt;0,BS34/24,""),"")</f>
       </c>
       <c r="X34" s="26"/>
       <c r="Y34" s="26"/>
       <c r="Z34" s="55"/>
       <c r="AA34" s="68">
-        <f t="shared" si="79"/>
+        <f>IF(E34&lt;&gt;"",IF(CA34&lt;&gt;0,CA34/24,""),"")</f>
       </c>
       <c r="AB34" s="26"/>
       <c r="AC34" s="26"/>
@@ -7696,7 +7761,7 @@
       <c r="AN34" s="72"/>
       <c r="AO34" s="55"/>
       <c r="AP34" s="73">
-        <f t="shared" si="10"/>
+        <f>IF(OR(AJ34&lt;&gt;"",AN34&lt;&gt;"",(BV34+BW34)&lt;&gt;0),IF(CD34=1,"","要"),IF(OR(S34&lt;&gt;"",W34&lt;&gt;"",AA34&lt;&gt;""),"申",""))</f>
       </c>
       <c r="AQ34" s="49"/>
       <c r="AR34" s="2"/>
@@ -7712,19 +7777,19 @@
       <c r="BB34" s="44"/>
       <c r="BC34" s="3"/>
       <c r="BD34" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BE34" s="11">
-        <f t="shared" si="62"/>
+        <f t="shared" si="48"/>
         <v>2026</v>
       </c>
       <c r="BF34" s="11">
-        <f t="shared" si="63"/>
+        <f t="shared" si="49"/>
         <v>9</v>
       </c>
       <c r="BG34" s="11" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>2026/9/15</v>
       </c>
       <c r="BH34" s="79">
@@ -7732,91 +7797,91 @@
         <v>0</v>
       </c>
       <c r="BI34" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ34" s="11">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BK34" s="80">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BL34" s="16">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="BM34" s="31">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="BN34" s="81">
+        <f t="shared" ref="BN34:BQ34" si="78">TEXT(MAX(0,MIN($BM34,BN$7)-MAX($BL34,BN$6)),"h:mm")*24</f>
+        <v>0</v>
+      </c>
+      <c r="BO34" s="82">
+        <f t="shared" si="78"/>
+        <v>0</v>
+      </c>
+      <c r="BP34" s="82">
+        <f t="shared" si="78"/>
+        <v>0</v>
+      </c>
+      <c r="BQ34" s="82">
+        <f t="shared" si="78"/>
+        <v>0</v>
+      </c>
+      <c r="BR34" s="82">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BK34" s="80">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BL34" s="16">
+      <c r="BS34" s="82">
+        <f t="shared" ref="BS34:BT34" si="79">TEXT(MAX(0,MIN($BM34,BS$7)-MAX($BL34,BS$6)),"h:mm")*24</f>
+        <v>0</v>
+      </c>
+      <c r="BT34" s="83">
+        <f t="shared" si="79"/>
+        <v>0</v>
+      </c>
+      <c r="BU34" s="82">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BM34" s="31">
+      <c r="BV34" s="82">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="BN34" s="81">
-        <f t="shared" ref="BN34:BQ34" si="101">TEXT(MAX(0,MIN($BM34,BN$7)-MAX($BL34,BN$6)),"h:mm")*24</f>
-        <v>0</v>
-      </c>
-      <c r="BO34" s="82">
-        <f t="shared" si="101"/>
-        <v>0</v>
-      </c>
-      <c r="BP34" s="82">
-        <f t="shared" si="101"/>
-        <v>0</v>
-      </c>
-      <c r="BQ34" s="82">
-        <f t="shared" si="101"/>
-        <v>0</v>
-      </c>
-      <c r="BR34" s="82">
+      <c r="BW34" s="82">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="BX34" s="82">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="BS34" s="82">
-        <f t="shared" ref="BS34:BT34" si="102">TEXT(MAX(0,MIN($BM34,BS$7)-MAX($BL34,BS$6)),"h:mm")*24</f>
-        <v>0</v>
-      </c>
-      <c r="BT34" s="83">
-        <f t="shared" si="102"/>
-        <v>0</v>
-      </c>
-      <c r="BU34" s="82">
+      <c r="BY34" s="82">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BZ34" s="84">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="BV34" s="82">
+      <c r="CA34" s="84">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="BW34" s="82">
+      <c r="CB34" s="84">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="BX34" s="82">
+      <c r="CC34" s="82">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="BY34" s="82">
+      <c r="CD34" s="11">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BZ34" s="84">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="CA34" s="84">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="CB34" s="84">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CC34" s="82">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="CD34" s="11">
-        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="CE34" s="11"/>
@@ -7844,29 +7909,29 @@
       <c r="K35" s="66"/>
       <c r="L35" s="55"/>
       <c r="M35" s="67">
-        <f t="shared" ref="M35" si="103">IF(E35="","",IF((BO35+BQ35)=0,"",(BO35+BQ35)*60))</f>
+        <f>IF(E35="","",IF((BO35+BQ35)=0,"",(BO35+BQ35)*60))</f>
       </c>
       <c r="N35" s="55"/>
       <c r="O35" s="93">
-        <f t="shared" si="100"/>
+        <f>IF(E35&lt;&gt;"",IF(BU35&lt;&gt;0,BU35/24,""),"")</f>
       </c>
       <c r="P35" s="26"/>
       <c r="Q35" s="26"/>
       <c r="R35" s="55"/>
       <c r="S35" s="68">
-        <f t="shared" si="61"/>
+        <f>IF(E35&lt;&gt;"",IF(BY35&lt;&gt;0,BY35/24,""),"")</f>
       </c>
       <c r="T35" s="26"/>
       <c r="U35" s="26"/>
       <c r="V35" s="55"/>
       <c r="W35" s="68">
-        <f t="shared" si="8"/>
+        <f>IF(E35&lt;&gt;"",IF(BS35&lt;&gt;0,BS35/24,""),"")</f>
       </c>
       <c r="X35" s="26"/>
       <c r="Y35" s="26"/>
       <c r="Z35" s="55"/>
       <c r="AA35" s="68">
-        <f t="shared" si="79"/>
+        <f>IF(E35&lt;&gt;"",IF(CA35&lt;&gt;0,CA35/24,""),"")</f>
       </c>
       <c r="AB35" s="26"/>
       <c r="AC35" s="26"/>
@@ -7883,7 +7948,7 @@
       <c r="AN35" s="72"/>
       <c r="AO35" s="55"/>
       <c r="AP35" s="73">
-        <f t="shared" si="10"/>
+        <f>IF(OR(AJ35&lt;&gt;"",AN35&lt;&gt;"",(BV35+BW35)&lt;&gt;0),IF(CD35=1,"","要"),IF(OR(S35&lt;&gt;"",W35&lt;&gt;"",AA35&lt;&gt;""),"申",""))</f>
       </c>
       <c r="AQ35" s="49"/>
       <c r="AR35" s="2"/>
@@ -7899,19 +7964,19 @@
       <c r="BB35" s="44"/>
       <c r="BC35" s="3"/>
       <c r="BD35" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BE35" s="11">
-        <f t="shared" si="62"/>
+        <f t="shared" si="48"/>
         <v>2026</v>
       </c>
       <c r="BF35" s="11">
-        <f t="shared" si="63"/>
+        <f t="shared" si="49"/>
         <v>9</v>
       </c>
       <c r="BG35" s="11" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>2026/9/16</v>
       </c>
       <c r="BH35" s="79">
@@ -7919,91 +7984,91 @@
         <v>0</v>
       </c>
       <c r="BI35" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ35" s="11">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BK35" s="80">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BL35" s="16">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="BM35" s="31">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="BN35" s="81">
+        <f t="shared" ref="BN35:BQ35" si="80">TEXT(MAX(0,MIN($BM35,BN$7)-MAX($BL35,BN$6)),"h:mm")*24</f>
+        <v>0</v>
+      </c>
+      <c r="BO35" s="82">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="BP35" s="82">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="BQ35" s="82">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="BR35" s="82">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BK35" s="80">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BL35" s="16">
+      <c r="BS35" s="82">
+        <f t="shared" ref="BS35:BT35" si="81">TEXT(MAX(0,MIN($BM35,BS$7)-MAX($BL35,BS$6)),"h:mm")*24</f>
+        <v>0</v>
+      </c>
+      <c r="BT35" s="83">
+        <f t="shared" si="81"/>
+        <v>0</v>
+      </c>
+      <c r="BU35" s="82">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BM35" s="31">
+      <c r="BV35" s="82">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="BN35" s="81">
-        <f t="shared" ref="BN35:BQ35" si="104">TEXT(MAX(0,MIN($BM35,BN$7)-MAX($BL35,BN$6)),"h:mm")*24</f>
-        <v>0</v>
-      </c>
-      <c r="BO35" s="82">
-        <f t="shared" si="104"/>
-        <v>0</v>
-      </c>
-      <c r="BP35" s="82">
-        <f t="shared" si="104"/>
-        <v>0</v>
-      </c>
-      <c r="BQ35" s="82">
-        <f t="shared" si="104"/>
-        <v>0</v>
-      </c>
-      <c r="BR35" s="82">
+      <c r="BW35" s="82">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="BX35" s="82">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="BS35" s="82">
-        <f t="shared" ref="BS35:BT35" si="105">TEXT(MAX(0,MIN($BM35,BS$7)-MAX($BL35,BS$6)),"h:mm")*24</f>
-        <v>0</v>
-      </c>
-      <c r="BT35" s="83">
-        <f t="shared" si="105"/>
-        <v>0</v>
-      </c>
-      <c r="BU35" s="82">
+      <c r="BY35" s="82">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BZ35" s="84">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="BV35" s="82">
+      <c r="CA35" s="84">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="BW35" s="82">
+      <c r="CB35" s="84">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="BX35" s="82">
+      <c r="CC35" s="82">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="BY35" s="82">
+      <c r="CD35" s="11">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BZ35" s="84">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="CA35" s="84">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="CB35" s="84">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CC35" s="82">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="CD35" s="11">
-        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="CE35" s="11"/>
@@ -8030,21 +8095,31 @@
       <c r="J36" s="65"/>
       <c r="K36" s="66"/>
       <c r="L36" s="55"/>
-      <c r="M36" s="67"/>
+      <c r="M36" s="67">
+        <f>IF(E36="","",IF((BO36+BQ36)=0,"",(BO36+BQ36)*60))</f>
+      </c>
       <c r="N36" s="55"/>
-      <c r="O36" s="68"/>
+      <c r="O36" s="68">
+        <f>IF(E36&lt;&gt;"",IF(BU36&lt;&gt;0,BU36/24,""),"")</f>
+      </c>
       <c r="P36" s="26"/>
       <c r="Q36" s="26"/>
       <c r="R36" s="55"/>
-      <c r="S36" s="68"/>
+      <c r="S36" s="68">
+        <f>IF(E36&lt;&gt;"",IF(BY36&lt;&gt;0,BY36/24,""),"")</f>
+      </c>
       <c r="T36" s="26"/>
       <c r="U36" s="26"/>
       <c r="V36" s="55"/>
-      <c r="W36" s="68"/>
+      <c r="W36" s="68">
+        <f>IF(E36&lt;&gt;"",IF(BS36&lt;&gt;0,BS36/24,""),"")</f>
+      </c>
       <c r="X36" s="26"/>
       <c r="Y36" s="26"/>
       <c r="Z36" s="55"/>
-      <c r="AA36" s="68"/>
+      <c r="AA36" s="68">
+        <f>IF(E36&lt;&gt;"",IF(CA36&lt;&gt;0,CA36/24,""),"")</f>
+      </c>
       <c r="AB36" s="26"/>
       <c r="AC36" s="26"/>
       <c r="AD36" s="55"/>
@@ -8060,7 +8135,7 @@
       <c r="AN36" s="72"/>
       <c r="AO36" s="55"/>
       <c r="AP36" s="73">
-        <f t="shared" si="10"/>
+        <f>IF(OR(AJ36&lt;&gt;"",AN36&lt;&gt;"",(BV36+BW36)&lt;&gt;0),IF(CD36=1,"","要"),IF(OR(S36&lt;&gt;"",W36&lt;&gt;"",AA36&lt;&gt;""),"申",""))</f>
       </c>
       <c r="AQ36" s="49"/>
       <c r="AR36" s="2"/>
@@ -8076,19 +8151,19 @@
       <c r="BB36" s="44"/>
       <c r="BC36" s="3"/>
       <c r="BD36" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BE36" s="11">
-        <f t="shared" si="62"/>
+        <f t="shared" si="48"/>
         <v>2026</v>
       </c>
       <c r="BF36" s="11">
-        <f t="shared" si="63"/>
+        <f t="shared" si="49"/>
         <v>9</v>
       </c>
       <c r="BG36" s="11" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>2026/9/17</v>
       </c>
       <c r="BH36" s="79">
@@ -8096,91 +8171,91 @@
         <v>0</v>
       </c>
       <c r="BI36" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ36" s="11">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BK36" s="80">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BL36" s="16">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="BM36" s="31">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="BN36" s="81">
+        <f t="shared" ref="BN36:BQ36" si="82">TEXT(MAX(0,MIN($BM36,BN$7)-MAX($BL36,BN$6)),"h:mm")*24</f>
+        <v>0</v>
+      </c>
+      <c r="BO36" s="82">
+        <f t="shared" si="82"/>
+        <v>0</v>
+      </c>
+      <c r="BP36" s="82">
+        <f t="shared" si="82"/>
+        <v>0</v>
+      </c>
+      <c r="BQ36" s="82">
+        <f t="shared" si="82"/>
+        <v>0</v>
+      </c>
+      <c r="BR36" s="82">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BK36" s="80">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BL36" s="16">
+      <c r="BS36" s="82">
+        <f t="shared" ref="BS36:BT36" si="83">TEXT(MAX(0,MIN($BM36,BS$7)-MAX($BL36,BS$6)),"h:mm")*24</f>
+        <v>0</v>
+      </c>
+      <c r="BT36" s="83">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+      <c r="BU36" s="82">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BM36" s="31">
+      <c r="BV36" s="82">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="BN36" s="81">
-        <f t="shared" ref="BN36:BQ36" si="106">TEXT(MAX(0,MIN($BM36,BN$7)-MAX($BL36,BN$6)),"h:mm")*24</f>
-        <v>0</v>
-      </c>
-      <c r="BO36" s="82">
-        <f t="shared" si="106"/>
-        <v>0</v>
-      </c>
-      <c r="BP36" s="82">
-        <f t="shared" si="106"/>
-        <v>0</v>
-      </c>
-      <c r="BQ36" s="82">
-        <f t="shared" si="106"/>
-        <v>0</v>
-      </c>
-      <c r="BR36" s="82">
+      <c r="BW36" s="82">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="BX36" s="82">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="BS36" s="82">
-        <f t="shared" ref="BS36:BT36" si="107">TEXT(MAX(0,MIN($BM36,BS$7)-MAX($BL36,BS$6)),"h:mm")*24</f>
-        <v>0</v>
-      </c>
-      <c r="BT36" s="83">
-        <f t="shared" si="107"/>
-        <v>0</v>
-      </c>
-      <c r="BU36" s="82">
+      <c r="BY36" s="82">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BZ36" s="84">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="BV36" s="82">
+      <c r="CA36" s="84">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="BW36" s="82">
+      <c r="CB36" s="84">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="BX36" s="82">
+      <c r="CC36" s="82">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="BY36" s="82">
+      <c r="CD36" s="11">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BZ36" s="84">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="CA36" s="84">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="CB36" s="84">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CC36" s="82">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="CD36" s="11">
-        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="CE36" s="11"/>
@@ -8207,21 +8282,31 @@
       <c r="J37" s="65"/>
       <c r="K37" s="66"/>
       <c r="L37" s="55"/>
-      <c r="M37" s="67"/>
+      <c r="M37" s="67">
+        <f>IF(E37="","",IF((BO37+BQ37)=0,"",(BO37+BQ37)*60))</f>
+      </c>
       <c r="N37" s="55"/>
-      <c r="O37" s="68"/>
+      <c r="O37" s="68">
+        <f>IF(E37&lt;&gt;"",IF(BU37&lt;&gt;0,BU37/24,""),"")</f>
+      </c>
       <c r="P37" s="26"/>
       <c r="Q37" s="26"/>
       <c r="R37" s="55"/>
-      <c r="S37" s="68"/>
+      <c r="S37" s="68">
+        <f>IF(E37&lt;&gt;"",IF(BY37&lt;&gt;0,BY37/24,""),"")</f>
+      </c>
       <c r="T37" s="26"/>
       <c r="U37" s="26"/>
       <c r="V37" s="55"/>
-      <c r="W37" s="68"/>
+      <c r="W37" s="68">
+        <f>IF(E37&lt;&gt;"",IF(BS37&lt;&gt;0,BS37/24,""),"")</f>
+      </c>
       <c r="X37" s="26"/>
       <c r="Y37" s="26"/>
       <c r="Z37" s="55"/>
-      <c r="AA37" s="68"/>
+      <c r="AA37" s="68">
+        <f>IF(E37&lt;&gt;"",IF(CA37&lt;&gt;0,CA37/24,""),"")</f>
+      </c>
       <c r="AB37" s="26"/>
       <c r="AC37" s="26"/>
       <c r="AD37" s="55"/>
@@ -8237,7 +8322,7 @@
       <c r="AN37" s="72"/>
       <c r="AO37" s="55"/>
       <c r="AP37" s="73">
-        <f t="shared" si="10"/>
+        <f>IF(OR(AJ37&lt;&gt;"",AN37&lt;&gt;"",(BV37+BW37)&lt;&gt;0),IF(CD37=1,"","要"),IF(OR(S37&lt;&gt;"",W37&lt;&gt;"",AA37&lt;&gt;""),"申",""))</f>
       </c>
       <c r="AQ37" s="49"/>
       <c r="AR37" s="2"/>
@@ -8253,19 +8338,19 @@
       <c r="BB37" s="44"/>
       <c r="BC37" s="3"/>
       <c r="BD37" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BE37" s="11">
-        <f t="shared" si="62"/>
+        <f t="shared" si="48"/>
         <v>2026</v>
       </c>
       <c r="BF37" s="11">
-        <f t="shared" si="63"/>
+        <f t="shared" si="49"/>
         <v>9</v>
       </c>
       <c r="BG37" s="11" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>2026/9/18</v>
       </c>
       <c r="BH37" s="79">
@@ -8273,91 +8358,91 @@
         <v>0</v>
       </c>
       <c r="BI37" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ37" s="11">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BK37" s="80">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BL37" s="16">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="BM37" s="31">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="BN37" s="81">
+        <f t="shared" ref="BN37:BQ37" si="84">TEXT(MAX(0,MIN($BM37,BN$7)-MAX($BL37,BN$6)),"h:mm")*24</f>
+        <v>0</v>
+      </c>
+      <c r="BO37" s="82">
+        <f t="shared" si="84"/>
+        <v>0</v>
+      </c>
+      <c r="BP37" s="82">
+        <f t="shared" si="84"/>
+        <v>0</v>
+      </c>
+      <c r="BQ37" s="82">
+        <f t="shared" si="84"/>
+        <v>0</v>
+      </c>
+      <c r="BR37" s="82">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BK37" s="80">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BL37" s="16">
+      <c r="BS37" s="82">
+        <f t="shared" ref="BS37:BT37" si="85">TEXT(MAX(0,MIN($BM37,BS$7)-MAX($BL37,BS$6)),"h:mm")*24</f>
+        <v>0</v>
+      </c>
+      <c r="BT37" s="83">
+        <f t="shared" si="85"/>
+        <v>0</v>
+      </c>
+      <c r="BU37" s="82">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BM37" s="31">
+      <c r="BV37" s="82">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="BN37" s="81">
-        <f t="shared" ref="BN37:BQ37" si="108">TEXT(MAX(0,MIN($BM37,BN$7)-MAX($BL37,BN$6)),"h:mm")*24</f>
-        <v>0</v>
-      </c>
-      <c r="BO37" s="82">
-        <f t="shared" si="108"/>
-        <v>0</v>
-      </c>
-      <c r="BP37" s="82">
-        <f t="shared" si="108"/>
-        <v>0</v>
-      </c>
-      <c r="BQ37" s="82">
-        <f t="shared" si="108"/>
-        <v>0</v>
-      </c>
-      <c r="BR37" s="82">
+      <c r="BW37" s="82">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="BX37" s="82">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="BS37" s="82">
-        <f t="shared" ref="BS37:BT37" si="109">TEXT(MAX(0,MIN($BM37,BS$7)-MAX($BL37,BS$6)),"h:mm")*24</f>
-        <v>0</v>
-      </c>
-      <c r="BT37" s="83">
-        <f t="shared" si="109"/>
-        <v>0</v>
-      </c>
-      <c r="BU37" s="82">
+      <c r="BY37" s="82">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BZ37" s="84">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="BV37" s="82">
+      <c r="CA37" s="84">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="BW37" s="82">
+      <c r="CB37" s="84">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="BX37" s="82">
+      <c r="CC37" s="82">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="BY37" s="82">
+      <c r="CD37" s="11">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BZ37" s="84">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="CA37" s="84">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="CB37" s="84">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CC37" s="82">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="CD37" s="11">
-        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="CE37" s="11"/>
@@ -8386,21 +8471,31 @@
       <c r="J38" s="65"/>
       <c r="K38" s="66"/>
       <c r="L38" s="55"/>
-      <c r="M38" s="67"/>
+      <c r="M38" s="67">
+        <f>IF(E38="","",IF((BO38+BQ38)=0,"",(BO38+BQ38)*60))</f>
+      </c>
       <c r="N38" s="55"/>
-      <c r="O38" s="93"/>
+      <c r="O38" s="93">
+        <f>IF(E38&lt;&gt;"",IF(BU38&lt;&gt;0,BU38/24,""),"")</f>
+      </c>
       <c r="P38" s="26"/>
       <c r="Q38" s="26"/>
       <c r="R38" s="55"/>
-      <c r="S38" s="68"/>
+      <c r="S38" s="68">
+        <f>IF(E38&lt;&gt;"",IF(BY38&lt;&gt;0,BY38/24,""),"")</f>
+      </c>
       <c r="T38" s="26"/>
       <c r="U38" s="26"/>
       <c r="V38" s="55"/>
-      <c r="W38" s="68"/>
+      <c r="W38" s="68">
+        <f>IF(E38&lt;&gt;"",IF(BS38&lt;&gt;0,BS38/24,""),"")</f>
+      </c>
       <c r="X38" s="26"/>
       <c r="Y38" s="26"/>
       <c r="Z38" s="55"/>
-      <c r="AA38" s="68"/>
+      <c r="AA38" s="68">
+        <f>IF(E38&lt;&gt;"",IF(CA38&lt;&gt;0,CA38/24,""),"")</f>
+      </c>
       <c r="AB38" s="26"/>
       <c r="AC38" s="26"/>
       <c r="AD38" s="55"/>
@@ -8416,7 +8511,7 @@
       <c r="AN38" s="72"/>
       <c r="AO38" s="55"/>
       <c r="AP38" s="73">
-        <f t="shared" si="10"/>
+        <f>IF(OR(AJ38&lt;&gt;"",AN38&lt;&gt;"",(BV38+BW38)&lt;&gt;0),IF(CD38=1,"","要"),IF(OR(S38&lt;&gt;"",W38&lt;&gt;"",AA38&lt;&gt;""),"申",""))</f>
       </c>
       <c r="AQ38" s="49"/>
       <c r="AR38" s="2"/>
@@ -8432,19 +8527,19 @@
       <c r="BB38" s="44"/>
       <c r="BC38" s="3"/>
       <c r="BD38" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BE38" s="11">
-        <f t="shared" si="62"/>
+        <f t="shared" si="48"/>
         <v>2026</v>
       </c>
       <c r="BF38" s="11">
-        <f t="shared" si="63"/>
+        <f t="shared" si="49"/>
         <v>9</v>
       </c>
       <c r="BG38" s="11" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>2026/9/19</v>
       </c>
       <c r="BH38" s="79">
@@ -8452,91 +8547,91 @@
         <v>0</v>
       </c>
       <c r="BI38" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ38" s="11">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BK38" s="80">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BL38" s="16">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="BM38" s="31">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="BN38" s="81">
+        <f t="shared" ref="BN38:BQ38" si="86">TEXT(MAX(0,MIN($BM38,BN$7)-MAX($BL38,BN$6)),"h:mm")*24</f>
+        <v>0</v>
+      </c>
+      <c r="BO38" s="82">
+        <f t="shared" si="86"/>
+        <v>0</v>
+      </c>
+      <c r="BP38" s="82">
+        <f t="shared" si="86"/>
+        <v>0</v>
+      </c>
+      <c r="BQ38" s="82">
+        <f t="shared" si="86"/>
+        <v>0</v>
+      </c>
+      <c r="BR38" s="82">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BK38" s="80">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BL38" s="16">
+      <c r="BS38" s="82">
+        <f t="shared" ref="BS38:BT38" si="87">TEXT(MAX(0,MIN($BM38,BS$7)-MAX($BL38,BS$6)),"h:mm")*24</f>
+        <v>0</v>
+      </c>
+      <c r="BT38" s="83">
+        <f t="shared" si="87"/>
+        <v>0</v>
+      </c>
+      <c r="BU38" s="82">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BM38" s="31">
+      <c r="BV38" s="82">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="BN38" s="81">
-        <f t="shared" ref="BN38:BQ38" si="110">TEXT(MAX(0,MIN($BM38,BN$7)-MAX($BL38,BN$6)),"h:mm")*24</f>
-        <v>0</v>
-      </c>
-      <c r="BO38" s="82">
-        <f t="shared" si="110"/>
-        <v>0</v>
-      </c>
-      <c r="BP38" s="82">
-        <f t="shared" si="110"/>
-        <v>0</v>
-      </c>
-      <c r="BQ38" s="82">
-        <f t="shared" si="110"/>
-        <v>0</v>
-      </c>
-      <c r="BR38" s="82">
+      <c r="BW38" s="82">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="BX38" s="82">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="BS38" s="82">
-        <f t="shared" ref="BS38:BT38" si="111">TEXT(MAX(0,MIN($BM38,BS$7)-MAX($BL38,BS$6)),"h:mm")*24</f>
-        <v>0</v>
-      </c>
-      <c r="BT38" s="83">
-        <f t="shared" si="111"/>
-        <v>0</v>
-      </c>
-      <c r="BU38" s="82">
+      <c r="BY38" s="82">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BZ38" s="84">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="BV38" s="82">
+      <c r="CA38" s="84">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="BW38" s="82">
+      <c r="CB38" s="84">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="BX38" s="82">
+      <c r="CC38" s="82">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="BY38" s="82">
+      <c r="CD38" s="11">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BZ38" s="84">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="CA38" s="84">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="CB38" s="84">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CC38" s="82">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="CD38" s="11">
-        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="CE38" s="11"/>
@@ -8565,21 +8660,31 @@
       <c r="J39" s="65"/>
       <c r="K39" s="66"/>
       <c r="L39" s="55"/>
-      <c r="M39" s="67"/>
+      <c r="M39" s="67">
+        <f>IF(E39="","",IF((BO39+BQ39)=0,"",(BO39+BQ39)*60))</f>
+      </c>
       <c r="N39" s="55"/>
-      <c r="O39" s="68"/>
+      <c r="O39" s="68">
+        <f>IF(E39&lt;&gt;"",IF(BU39&lt;&gt;0,BU39/24,""),"")</f>
+      </c>
       <c r="P39" s="26"/>
       <c r="Q39" s="26"/>
       <c r="R39" s="55"/>
-      <c r="S39" s="68"/>
+      <c r="S39" s="68">
+        <f>IF(E39&lt;&gt;"",IF(BY39&lt;&gt;0,BY39/24,""),"")</f>
+      </c>
       <c r="T39" s="26"/>
       <c r="U39" s="26"/>
       <c r="V39" s="55"/>
-      <c r="W39" s="68"/>
+      <c r="W39" s="68">
+        <f>IF(E39&lt;&gt;"",IF(BS39&lt;&gt;0,BS39/24,""),"")</f>
+      </c>
       <c r="X39" s="26"/>
       <c r="Y39" s="26"/>
       <c r="Z39" s="55"/>
-      <c r="AA39" s="68"/>
+      <c r="AA39" s="68">
+        <f>IF(E39&lt;&gt;"",IF(CA39&lt;&gt;0,CA39/24,""),"")</f>
+      </c>
       <c r="AB39" s="26"/>
       <c r="AC39" s="26"/>
       <c r="AD39" s="55"/>
@@ -8595,7 +8700,7 @@
       <c r="AN39" s="72"/>
       <c r="AO39" s="55"/>
       <c r="AP39" s="73">
-        <f t="shared" si="10"/>
+        <f>IF(OR(AJ39&lt;&gt;"",AN39&lt;&gt;"",(BV39+BW39)&lt;&gt;0),IF(CD39=1,"","要"),IF(OR(S39&lt;&gt;"",W39&lt;&gt;"",AA39&lt;&gt;""),"申",""))</f>
       </c>
       <c r="AQ39" s="47"/>
       <c r="AR39" s="14"/>
@@ -8611,19 +8716,19 @@
       <c r="BB39" s="48"/>
       <c r="BC39" s="3"/>
       <c r="BD39" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BE39" s="11">
-        <f t="shared" si="62"/>
+        <f t="shared" si="48"/>
         <v>2026</v>
       </c>
       <c r="BF39" s="11">
-        <f t="shared" si="63"/>
+        <f t="shared" si="49"/>
         <v>9</v>
       </c>
       <c r="BG39" s="11" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>2026/9/20</v>
       </c>
       <c r="BH39" s="79">
@@ -8631,91 +8736,91 @@
         <v>0</v>
       </c>
       <c r="BI39" s="97">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ39" s="97">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BK39" s="98">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BL39" s="99">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="BM39" s="100">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="BN39" s="101">
+        <f t="shared" ref="BN39:BQ39" si="88">TEXT(MAX(0,MIN($BM39,BN$7)-MAX($BL39,BN$6)),"h:mm")*24</f>
+        <v>0</v>
+      </c>
+      <c r="BO39" s="102">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="BP39" s="102">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="BQ39" s="102">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="BR39" s="102">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BK39" s="98">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BL39" s="99">
+      <c r="BS39" s="102">
+        <f t="shared" ref="BS39:BT39" si="89">TEXT(MAX(0,MIN($BM39,BS$7)-MAX($BL39,BS$6)),"h:mm")*24</f>
+        <v>0</v>
+      </c>
+      <c r="BT39" s="103">
+        <f t="shared" si="89"/>
+        <v>0</v>
+      </c>
+      <c r="BU39" s="102">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BM39" s="100">
+      <c r="BV39" s="102">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="BN39" s="101">
-        <f t="shared" ref="BN39:BQ39" si="112">TEXT(MAX(0,MIN($BM39,BN$7)-MAX($BL39,BN$6)),"h:mm")*24</f>
-        <v>0</v>
-      </c>
-      <c r="BO39" s="102">
-        <f t="shared" si="112"/>
-        <v>0</v>
-      </c>
-      <c r="BP39" s="102">
-        <f t="shared" si="112"/>
-        <v>0</v>
-      </c>
-      <c r="BQ39" s="102">
-        <f t="shared" si="112"/>
-        <v>0</v>
-      </c>
-      <c r="BR39" s="102">
+      <c r="BW39" s="102">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="BX39" s="102">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="BS39" s="102">
-        <f t="shared" ref="BS39:BT39" si="113">TEXT(MAX(0,MIN($BM39,BS$7)-MAX($BL39,BS$6)),"h:mm")*24</f>
-        <v>0</v>
-      </c>
-      <c r="BT39" s="103">
-        <f t="shared" si="113"/>
-        <v>0</v>
-      </c>
-      <c r="BU39" s="102">
+      <c r="BY39" s="102">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BZ39" s="104">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="BV39" s="102">
+      <c r="CA39" s="104">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="BW39" s="102">
+      <c r="CB39" s="104">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="BX39" s="102">
+      <c r="CC39" s="102">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="BY39" s="102">
+      <c r="CD39" s="11">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BZ39" s="104">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="CA39" s="104">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="CB39" s="104">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CC39" s="102">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="CD39" s="11">
-        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="CE39" s="11"/>
@@ -8825,32 +8930,32 @@
       <c r="BS40" s="82"/>
       <c r="BT40" s="82"/>
       <c r="BU40" s="82">
-        <f t="shared" ref="BU40:BW40" si="114">SUM(BU9:BU39)</f>
+        <f t="shared" ref="BU40:BW40" si="90">SUM(BU9:BU39)</f>
         <v>121</v>
       </c>
       <c r="BV40" s="82">
-        <f t="shared" si="114"/>
+        <f t="shared" si="90"/>
         <v>3</v>
       </c>
       <c r="BW40" s="82">
-        <f t="shared" si="114"/>
+        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="BX40" s="82"/>
       <c r="BY40" s="82">
-        <f t="shared" ref="BY40:CB40" si="115">SUM(BY9:BY39)</f>
+        <f t="shared" ref="BY40:CB40" si="91">SUM(BY9:BY39)</f>
         <v>0.5</v>
       </c>
       <c r="BZ40" s="82">
-        <f t="shared" si="115"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="CA40" s="82">
-        <f t="shared" si="115"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="CB40" s="82">
-        <f t="shared" si="115"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="CC40" s="82"/>
